--- a/Base Limpa.xlsx
+++ b/Base Limpa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corpclarobr-my.sharepoint.com/personal/bruno_mandarsilva_claro_com_br/Documents/Documentos/dashboard-logistica/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4706" documentId="8_{C973436A-53F7-4C3D-9821-DB0945EE825D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59665F42-C56E-4949-A156-DE491FF5C93D}"/>
+  <xr:revisionPtr revIDLastSave="4712" documentId="8_{C973436A-53F7-4C3D-9821-DB0945EE825D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61B240A1-A567-46DC-B736-C1A686A7394A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="252">
   <si>
     <t>Prioridade</t>
   </si>
@@ -865,12 +865,21 @@
   <si>
     <t>Bernardino.lagoa@claro.com.br,Bruno.Feijo@claro.com.br</t>
   </si>
+  <si>
+    <t>LOG-64</t>
+  </si>
+  <si>
+    <t>Teste</t>
+  </si>
+  <si>
+    <t>TESTE ATUALIZAÇÃO</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -895,6 +904,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1314,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3763512-A9A0-4D95-8469-18E3F7F25B1D}">
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
@@ -3948,7 +3963,49 @@
         <v>142</v>
       </c>
     </row>
+    <row r="65" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>249</v>
+      </c>
+      <c r="B65" t="s">
+        <v>250</v>
+      </c>
+      <c r="C65" t="s">
+        <v>4</v>
+      </c>
+      <c r="D65" t="s">
+        <v>183</v>
+      </c>
+      <c r="E65" t="s">
+        <v>142</v>
+      </c>
+      <c r="F65" t="s">
+        <v>1</v>
+      </c>
+      <c r="G65" s="11">
+        <v>46204</v>
+      </c>
+      <c r="H65" s="11">
+        <v>46568</v>
+      </c>
+      <c r="I65" t="s">
+        <v>146</v>
+      </c>
+      <c r="K65" t="s">
+        <v>251</v>
+      </c>
+      <c r="L65" s="11">
+        <v>46215</v>
+      </c>
+      <c r="M65" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="N65" t="s">
+        <v>142</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1" display="mailto:Diego.RochaSantos@claro.com.br" xr:uid="{D0338977-67C9-4B5B-9644-A9AE82FD389E}"/>
     <hyperlink ref="M3" r:id="rId2" xr:uid="{E09EF2DC-D941-4EBA-B94F-54B57EC16277}"/>
@@ -4013,6 +4070,7 @@
     <hyperlink ref="M62" r:id="rId61" display="mailto:Bernardino.lagoa@claro.com.br" xr:uid="{5164CF39-CB99-46E2-98AB-6925F0CCED92}"/>
     <hyperlink ref="M63" r:id="rId62" display="mailto:Bernardino.lagoa@claro.com.br,Bruno.Feijo@claro.com.br" xr:uid="{4606E8EE-F97F-4D0A-A1E5-BA36AA180B25}"/>
     <hyperlink ref="M64" r:id="rId63" display="mailto:paulo.rocha@claro.com.br" xr:uid="{E0A00782-EA79-4CE3-94A7-F14E6B4CD6D9}"/>
+    <hyperlink ref="M65" r:id="rId64" display="mailto:paulo.rocha@claro.com.br" xr:uid="{25BB1CD6-87C3-4FE2-928F-94D7442F0426}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4028,17 +4086,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="48a4df2c-25c0-4bd5-9ad3-969cdc4eb0ad">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fe5609ce-cb92-4045-944c-c105fdf4b20b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006A0F678961C25F42A60818D832EED552" ma:contentTypeVersion="15" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="dc2a7ab8599bba470a78deafa62af16c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="48a4df2c-25c0-4bd5-9ad3-969cdc4eb0ad" xmlns:ns3="fe5609ce-cb92-4045-944c-c105fdf4b20b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ffd182497d787a9e927f0f89c1000013" ns2:_="" ns3:_="">
     <xsd:import namespace="48a4df2c-25c0-4bd5-9ad3-969cdc4eb0ad"/>
@@ -4273,6 +4320,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="48a4df2c-25c0-4bd5-9ad3-969cdc4eb0ad">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fe5609ce-cb92-4045-944c-c105fdf4b20b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{421192A4-7E63-4E34-BFD9-A0D092033413}">
   <ds:schemaRefs>
@@ -4282,17 +4340,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F58F0C4-7563-4480-B156-7EBAF344CD6A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="48a4df2c-25c0-4bd5-9ad3-969cdc4eb0ad"/>
-    <ds:schemaRef ds:uri="fe5609ce-cb92-4045-944c-c105fdf4b20b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4FC87EE-D01F-4F08-8D84-C3D05E1D5A3A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4309,4 +4356,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F58F0C4-7563-4480-B156-7EBAF344CD6A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="48a4df2c-25c0-4bd5-9ad3-969cdc4eb0ad"/>
+    <ds:schemaRef ds:uri="fe5609ce-cb92-4045-944c-c105fdf4b20b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Base Limpa.xlsx
+++ b/Base Limpa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corpclarobr-my.sharepoint.com/personal/bruno_mandarsilva_claro_com_br/Documents/Documentos/dashboard-logistica/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4712" documentId="8_{C973436A-53F7-4C3D-9821-DB0945EE825D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61B240A1-A567-46DC-B736-C1A686A7394A}"/>
+  <xr:revisionPtr revIDLastSave="4725" documentId="8_{C973436A-53F7-4C3D-9821-DB0945EE825D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2872E00B-344B-4FBB-87D2-877A08003732}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="250">
   <si>
     <t>Prioridade</t>
   </si>
@@ -701,10 +701,6 @@
 Prazo final de analises: 26/06/2026. Responsável: Leandro / Thiago</t>
   </si>
   <si>
-    <t>30/07 - Levantamento do Processo de Roteirização Atual, melhorias e impactos
-10/06 - Reunião agendada para entendimento do andamento do projeto</t>
-  </si>
-  <si>
     <t>1. iniciamos a análise e validação junto à SIC – Segurança Lógica Corporativa, que trouxe considerações positivas sobre a forma como estruturamos o projeto.
 2. Entrevista com todas as coordenações (finaliza em 07/08)</t>
   </si>
@@ -734,12 +730,6 @@
   <si>
     <t>1. Em estudo - Na busca de copatrocinio, diretoria não aprovou o investimento. Se aprovado pela diretoria: início das aquisições de caixas em JUL/26;
 2. 06/07/26 - Estimativa da DPR retornar com orçamento para injeção de Ecobox.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/06 - Definir quais projetos serão executados e o cronograma de implantação.
-04/06 - Apresentação do cronograma de atividades para 2026 pela Accenture.
-08/06 - A Accenture cancelou as últimas agendas de reunião sobre o projeto.
-Na reunião dessa semana, irei cobrar deles esse cronograma e atualizo o card em seguida. </t>
   </si>
   <si>
     <t>Jun/26: Confirmar recebimento dos Envelopes nos CDs;
@@ -866,13 +856,18 @@
     <t>Bernardino.lagoa@claro.com.br,Bruno.Feijo@claro.com.br</t>
   </si>
   <si>
-    <t>LOG-64</t>
-  </si>
-  <si>
-    <t>Teste</t>
-  </si>
-  <si>
-    <t>TESTE ATUALIZAÇÃO</t>
+    <t>SEM AÇÃO</t>
+  </si>
+  <si>
+    <t>30/06 - Estruturação da Calendarização Atual e Pontos de Melhorias e Impactos
+30/08 - Mapeamento da Capilaridade
+20/12 - Levantamento do retorno das aplicadas x retorno das melhorias</t>
+  </si>
+  <si>
+    <t>06/08 - Definir quais projetos serão executados e o cronograma de implantação
+13/08 - Apresentação do cronograma de atividades para 2026 pela Accenture
+21/08 - Definir premissas dos estudos
+31/12 - Acompanhar a implantação e demonstrar os ganhos.</t>
   </si>
 </sst>
 </file>
@@ -968,7 +963,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -999,15 +994,14 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hiperlink" xfId="3" builtinId="8"/>
@@ -1408,20 +1402,20 @@
       <c r="I2" t="s">
         <v>146</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="14" t="s">
         <v>184</v>
       </c>
       <c r="L2" s="7">
         <v>46203</v>
       </c>
-      <c r="M2" s="13" t="s">
-        <v>223</v>
+      <c r="M2" s="12" t="s">
+        <v>221</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="130.5" x14ac:dyDescent="0.35">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -1449,20 +1443,20 @@
       <c r="I3" t="s">
         <v>146</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="14" t="s">
         <v>198</v>
       </c>
       <c r="L3" s="7">
         <v>46184</v>
       </c>
-      <c r="M3" s="13" t="s">
-        <v>224</v>
+      <c r="M3" s="12" t="s">
+        <v>222</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="174" x14ac:dyDescent="0.35">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>87</v>
       </c>
@@ -1490,20 +1484,20 @@
       <c r="I4" t="s">
         <v>146</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="14" t="s">
         <v>199</v>
       </c>
       <c r="L4" s="7">
         <v>46185</v>
       </c>
-      <c r="M4" s="13" t="s">
-        <v>225</v>
+      <c r="M4" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="101.5" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>88</v>
       </c>
@@ -1531,20 +1525,20 @@
       <c r="I5" t="s">
         <v>147</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="14" t="s">
         <v>167</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="13" t="s">
-        <v>226</v>
+      <c r="M5" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="174" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>89</v>
       </c>
@@ -1572,14 +1566,14 @@
       <c r="I6" t="s">
         <v>146</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="14" t="s">
         <v>200</v>
       </c>
       <c r="L6" s="7">
         <v>46193</v>
       </c>
-      <c r="M6" s="13" t="s">
-        <v>227</v>
+      <c r="M6" s="12" t="s">
+        <v>225</v>
       </c>
       <c r="N6" s="10" t="s">
         <v>142</v>
@@ -1613,20 +1607,20 @@
       <c r="I7" t="s">
         <v>146</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="14" t="s">
         <v>185</v>
       </c>
       <c r="L7" s="7">
         <v>46183</v>
       </c>
-      <c r="M7" s="13" t="s">
-        <v>228</v>
+      <c r="M7" s="12" t="s">
+        <v>226</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="290" x14ac:dyDescent="0.35">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>91</v>
       </c>
@@ -1654,20 +1648,20 @@
       <c r="I8" t="s">
         <v>146</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="14" t="s">
         <v>201</v>
       </c>
       <c r="L8" s="7">
         <v>46204</v>
       </c>
-      <c r="M8" s="13" t="s">
-        <v>229</v>
+      <c r="M8" s="12" t="s">
+        <v>227</v>
       </c>
       <c r="N8" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>78</v>
       </c>
@@ -1695,20 +1689,20 @@
       <c r="I9" t="s">
         <v>146</v>
       </c>
-      <c r="K9" s="12" t="s">
+      <c r="K9" s="14" t="s">
         <v>202</v>
       </c>
       <c r="L9" s="7">
         <v>46183</v>
       </c>
-      <c r="M9" s="13" t="s">
-        <v>230</v>
+      <c r="M9" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="246.5" x14ac:dyDescent="0.35">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>92</v>
       </c>
@@ -1736,17 +1730,17 @@
       <c r="I10" t="s">
         <v>146</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" s="14" t="s">
         <v>203</v>
       </c>
       <c r="L10" s="7">
         <v>46189</v>
       </c>
-      <c r="M10" s="13" t="s">
-        <v>231</v>
+      <c r="M10" s="12" t="s">
+        <v>229</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="16" x14ac:dyDescent="0.35">
@@ -1777,20 +1771,20 @@
       <c r="I11" t="s">
         <v>146</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="14" t="s">
         <v>186</v>
       </c>
       <c r="L11" s="7">
         <v>46185</v>
       </c>
-      <c r="M11" s="13" t="s">
-        <v>226</v>
+      <c r="M11" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="101.5" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>94</v>
       </c>
@@ -1818,17 +1812,17 @@
       <c r="I12" t="s">
         <v>146</v>
       </c>
-      <c r="K12" s="12" t="s">
+      <c r="K12" s="14" t="s">
         <v>204</v>
       </c>
       <c r="L12" s="7">
         <v>46185</v>
       </c>
-      <c r="M12" s="13" t="s">
-        <v>232</v>
+      <c r="M12" s="12" t="s">
+        <v>230</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="16" x14ac:dyDescent="0.35">
@@ -1859,20 +1853,20 @@
       <c r="I13" t="s">
         <v>147</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="14" t="s">
         <v>152</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M13" s="13" t="s">
-        <v>233</v>
+      <c r="M13" s="12" t="s">
+        <v>231</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="261" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>96</v>
       </c>
@@ -1900,20 +1894,20 @@
       <c r="I14" t="s">
         <v>148</v>
       </c>
-      <c r="K14" s="12" t="s">
+      <c r="K14" s="14" t="s">
         <v>205</v>
       </c>
       <c r="L14" s="7">
         <v>46188</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>232</v>
+      <c r="M14" s="12" t="s">
+        <v>230</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="188.5" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>97</v>
       </c>
@@ -1941,20 +1935,20 @@
       <c r="I15" t="s">
         <v>146</v>
       </c>
-      <c r="K15" s="12" t="s">
+      <c r="K15" s="14" t="s">
         <v>206</v>
       </c>
       <c r="L15" s="7">
         <v>46231</v>
       </c>
-      <c r="M15" s="13" t="s">
-        <v>227</v>
+      <c r="M15" s="12" t="s">
+        <v>225</v>
       </c>
       <c r="N15" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>98</v>
       </c>
@@ -1982,20 +1976,20 @@
       <c r="I16" t="s">
         <v>146</v>
       </c>
-      <c r="K16" s="12" t="s">
+      <c r="K16" s="14" t="s">
         <v>207</v>
       </c>
       <c r="L16" s="7">
         <v>46199</v>
       </c>
-      <c r="M16" s="13" t="s">
-        <v>234</v>
+      <c r="M16" s="12" t="s">
+        <v>232</v>
       </c>
       <c r="N16" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="116" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>99</v>
       </c>
@@ -2023,20 +2017,20 @@
       <c r="I17" t="s">
         <v>149</v>
       </c>
-      <c r="K17" s="12" t="s">
-        <v>208</v>
+      <c r="K17" s="14" t="s">
+        <v>248</v>
       </c>
       <c r="L17" s="7">
-        <v>46233</v>
-      </c>
-      <c r="M17" s="13" t="s">
-        <v>235</v>
+        <v>46203</v>
+      </c>
+      <c r="M17" s="12" t="s">
+        <v>233</v>
       </c>
       <c r="N17" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>100</v>
       </c>
@@ -2064,14 +2058,14 @@
       <c r="I18" t="s">
         <v>148</v>
       </c>
-      <c r="K18" s="12" t="s">
+      <c r="K18" s="14" t="s">
         <v>168</v>
       </c>
       <c r="L18" s="7">
         <v>46209</v>
       </c>
-      <c r="M18" s="13" t="s">
-        <v>236</v>
+      <c r="M18" s="12" t="s">
+        <v>234</v>
       </c>
       <c r="N18" s="10" t="s">
         <v>142</v>
@@ -2105,17 +2099,17 @@
       <c r="I19" t="s">
         <v>147</v>
       </c>
-      <c r="K19" s="10" t="s">
+      <c r="K19" s="14" t="s">
         <v>187</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M19" s="13" t="s">
-        <v>237</v>
+      <c r="M19" s="12" t="s">
+        <v>235</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>142</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="16" x14ac:dyDescent="0.35">
@@ -2146,17 +2140,17 @@
       <c r="I20" t="s">
         <v>146</v>
       </c>
-      <c r="K20" s="10" t="s">
+      <c r="K20" s="14" t="s">
         <v>188</v>
       </c>
       <c r="L20" s="7">
         <v>46188</v>
       </c>
-      <c r="M20" s="13" t="s">
-        <v>238</v>
+      <c r="M20" s="12" t="s">
+        <v>236</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="16" x14ac:dyDescent="0.35">
@@ -2187,20 +2181,20 @@
       <c r="I21" t="s">
         <v>146</v>
       </c>
-      <c r="K21" s="10" t="s">
+      <c r="K21" s="14" t="s">
         <v>153</v>
       </c>
       <c r="L21" s="7">
         <v>46188</v>
       </c>
-      <c r="M21" s="13" t="s">
-        <v>239</v>
+      <c r="M21" s="12" t="s">
+        <v>237</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="145" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>104</v>
       </c>
@@ -2228,20 +2222,20 @@
       <c r="I22" t="s">
         <v>149</v>
       </c>
-      <c r="K22" s="12" t="s">
-        <v>209</v>
+      <c r="K22" s="14" t="s">
+        <v>208</v>
       </c>
       <c r="L22" s="7">
         <v>46188</v>
       </c>
-      <c r="M22" s="13" t="s">
-        <v>240</v>
+      <c r="M22" s="12" t="s">
+        <v>238</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="409.5" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -2269,17 +2263,17 @@
       <c r="I23" t="s">
         <v>149</v>
       </c>
-      <c r="K23" s="12" t="s">
-        <v>210</v>
+      <c r="K23" s="14" t="s">
+        <v>209</v>
       </c>
       <c r="L23" s="7">
         <v>46189</v>
       </c>
-      <c r="M23" s="13" t="s">
-        <v>226</v>
+      <c r="M23" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="16" x14ac:dyDescent="0.35">
@@ -2310,20 +2304,20 @@
       <c r="I24" t="s">
         <v>147</v>
       </c>
-      <c r="K24" s="10" t="s">
+      <c r="K24" s="14" t="s">
         <v>154</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M24" s="13" t="s">
-        <v>226</v>
+      <c r="M24" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="N24" s="10" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>106</v>
       </c>
@@ -2351,20 +2345,20 @@
       <c r="I25" t="s">
         <v>147</v>
       </c>
-      <c r="K25" s="12" t="s">
+      <c r="K25" s="14" t="s">
         <v>169</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M25" s="13" t="s">
-        <v>231</v>
+      <c r="M25" s="12" t="s">
+        <v>229</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="159.5" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>107</v>
       </c>
@@ -2392,20 +2386,20 @@
       <c r="I26" t="s">
         <v>147</v>
       </c>
-      <c r="K26" s="12" t="s">
+      <c r="K26" s="14" t="s">
         <v>170</v>
       </c>
       <c r="L26" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M26" s="13" t="s">
-        <v>230</v>
+      <c r="M26" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="N26" s="10" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="174" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>108</v>
       </c>
@@ -2433,20 +2427,20 @@
       <c r="I27" t="s">
         <v>146</v>
       </c>
-      <c r="K27" s="12" t="s">
-        <v>211</v>
+      <c r="K27" s="14" t="s">
+        <v>210</v>
       </c>
       <c r="L27" s="7">
         <v>46183</v>
       </c>
-      <c r="M27" s="13" t="s">
-        <v>241</v>
+      <c r="M27" s="12" t="s">
+        <v>239</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="246.5" x14ac:dyDescent="0.35">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>109</v>
       </c>
@@ -2474,17 +2468,17 @@
       <c r="I28" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="12" t="s">
+      <c r="K28" s="14" t="s">
         <v>171</v>
       </c>
       <c r="L28" s="7">
         <v>46171</v>
       </c>
-      <c r="M28" s="13" t="s">
-        <v>240</v>
+      <c r="M28" s="12" t="s">
+        <v>238</v>
       </c>
       <c r="N28" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="16" x14ac:dyDescent="0.35">
@@ -2515,20 +2509,20 @@
       <c r="I29" t="s">
         <v>146</v>
       </c>
-      <c r="K29" s="10" t="s">
+      <c r="K29" s="14" t="s">
         <v>189</v>
       </c>
       <c r="L29" s="7">
         <v>46188</v>
       </c>
-      <c r="M29" s="13" t="s">
-        <v>225</v>
+      <c r="M29" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="409.5" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>111</v>
       </c>
@@ -2556,20 +2550,20 @@
       <c r="I30" t="s">
         <v>149</v>
       </c>
-      <c r="K30" s="12" t="s">
-        <v>212</v>
+      <c r="K30" s="14" t="s">
+        <v>211</v>
       </c>
       <c r="L30" s="7">
         <v>46188</v>
       </c>
-      <c r="M30" s="13" t="s">
-        <v>233</v>
+      <c r="M30" s="12" t="s">
+        <v>231</v>
       </c>
       <c r="N30" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="188.5" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>112</v>
       </c>
@@ -2597,20 +2591,20 @@
       <c r="I31" t="s">
         <v>148</v>
       </c>
-      <c r="K31" s="12" t="s">
-        <v>213</v>
+      <c r="K31" s="14" t="s">
+        <v>212</v>
       </c>
       <c r="L31" s="7">
         <v>46203</v>
       </c>
-      <c r="M31" s="13" t="s">
-        <v>242</v>
+      <c r="M31" s="12" t="s">
+        <v>240</v>
       </c>
       <c r="N31" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>113</v>
       </c>
@@ -2638,20 +2632,20 @@
       <c r="I32" t="s">
         <v>146</v>
       </c>
-      <c r="K32" s="12" t="s">
-        <v>214</v>
+      <c r="K32" s="14" t="s">
+        <v>213</v>
       </c>
       <c r="L32" s="7">
         <v>46209</v>
       </c>
-      <c r="M32" s="13" t="s">
-        <v>232</v>
+      <c r="M32" s="12" t="s">
+        <v>230</v>
       </c>
       <c r="N32" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="290" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>114</v>
       </c>
@@ -2679,14 +2673,14 @@
       <c r="I33" t="s">
         <v>146</v>
       </c>
-      <c r="K33" s="12" t="s">
-        <v>215</v>
+      <c r="K33" s="14" t="s">
+        <v>249</v>
       </c>
       <c r="L33" s="7">
-        <v>46183</v>
-      </c>
-      <c r="M33" s="13" t="s">
-        <v>225</v>
+        <v>46240</v>
+      </c>
+      <c r="M33" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="N33" s="10" t="s">
         <v>142</v>
@@ -2720,17 +2714,17 @@
       <c r="I34" t="s">
         <v>147</v>
       </c>
-      <c r="K34" s="10" t="s">
+      <c r="K34" s="14" t="s">
         <v>155</v>
       </c>
       <c r="L34" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M34" s="13" t="s">
-        <v>237</v>
+      <c r="M34" s="12" t="s">
+        <v>235</v>
       </c>
       <c r="N34" s="10" t="s">
-        <v>143</v>
+        <v>247</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="16" x14ac:dyDescent="0.35">
@@ -2761,17 +2755,17 @@
       <c r="I35" t="s">
         <v>147</v>
       </c>
-      <c r="K35" s="10" t="s">
+      <c r="K35" s="14" t="s">
         <v>156</v>
       </c>
       <c r="L35" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M35" s="13" t="s">
-        <v>233</v>
+      <c r="M35" s="12" t="s">
+        <v>231</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>143</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="16" x14ac:dyDescent="0.35">
@@ -2802,20 +2796,20 @@
       <c r="I36" t="s">
         <v>148</v>
       </c>
-      <c r="K36" s="10" t="s">
+      <c r="K36" s="14" t="s">
         <v>190</v>
       </c>
       <c r="L36" s="7">
         <v>46190</v>
       </c>
-      <c r="M36" s="13" t="s">
-        <v>238</v>
+      <c r="M36" s="12" t="s">
+        <v>236</v>
       </c>
       <c r="N36" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="377" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>118</v>
       </c>
@@ -2843,14 +2837,14 @@
       <c r="I37" t="s">
         <v>148</v>
       </c>
-      <c r="K37" s="12" t="s">
-        <v>216</v>
+      <c r="K37" s="14" t="s">
+        <v>214</v>
       </c>
       <c r="L37" s="7">
         <v>46204</v>
       </c>
-      <c r="M37" s="13" t="s">
-        <v>243</v>
+      <c r="M37" s="12" t="s">
+        <v>241</v>
       </c>
       <c r="N37" s="10" t="s">
         <v>142</v>
@@ -2884,14 +2878,14 @@
       <c r="I38" t="s">
         <v>146</v>
       </c>
-      <c r="K38" s="10" t="s">
+      <c r="K38" s="14" t="s">
         <v>157</v>
       </c>
       <c r="L38" s="7">
         <v>46192</v>
       </c>
-      <c r="M38" s="13" t="s">
-        <v>244</v>
+      <c r="M38" s="12" t="s">
+        <v>242</v>
       </c>
       <c r="N38" s="10" t="s">
         <v>142</v>
@@ -2925,20 +2919,20 @@
       <c r="I39" t="s">
         <v>147</v>
       </c>
-      <c r="K39" s="10" t="s">
+      <c r="K39" s="14" t="s">
         <v>158</v>
       </c>
       <c r="L39" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M39" s="13" t="s">
-        <v>245</v>
+      <c r="M39" s="12" t="s">
+        <v>243</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>80</v>
       </c>
@@ -2966,17 +2960,17 @@
       <c r="I40" t="s">
         <v>146</v>
       </c>
-      <c r="K40" s="12" t="s">
-        <v>217</v>
+      <c r="K40" s="14" t="s">
+        <v>215</v>
       </c>
       <c r="L40" s="7">
         <v>46185</v>
       </c>
-      <c r="M40" s="13" t="s">
-        <v>230</v>
+      <c r="M40" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="N40" s="10" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="16" x14ac:dyDescent="0.35">
@@ -3007,17 +3001,17 @@
       <c r="I41" t="s">
         <v>147</v>
       </c>
-      <c r="K41" s="10" t="s">
+      <c r="K41" s="14" t="s">
         <v>159</v>
       </c>
       <c r="L41" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M41" s="13" t="s">
-        <v>227</v>
+      <c r="M41" s="12" t="s">
+        <v>225</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>143</v>
+        <v>247</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="16" x14ac:dyDescent="0.35">
@@ -3048,20 +3042,20 @@
       <c r="I42" t="s">
         <v>148</v>
       </c>
-      <c r="K42" s="10" t="s">
+      <c r="K42" s="14" t="s">
         <v>160</v>
       </c>
       <c r="L42" s="7">
         <v>46203</v>
       </c>
-      <c r="M42" s="13" t="s">
-        <v>226</v>
+      <c r="M42" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="N42" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>123</v>
       </c>
@@ -3089,17 +3083,17 @@
       <c r="I43" t="s">
         <v>146</v>
       </c>
-      <c r="K43" s="12" t="s">
+      <c r="K43" s="14" t="s">
         <v>172</v>
       </c>
       <c r="L43" s="7">
         <v>46173</v>
       </c>
-      <c r="M43" s="13" t="s">
-        <v>241</v>
+      <c r="M43" s="12" t="s">
+        <v>239</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="16" x14ac:dyDescent="0.35">
@@ -3130,17 +3124,17 @@
       <c r="I44" t="s">
         <v>147</v>
       </c>
-      <c r="K44" s="10" t="s">
+      <c r="K44" s="14" t="s">
         <v>161</v>
       </c>
       <c r="L44" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M44" s="13" t="s">
-        <v>245</v>
+      <c r="M44" s="12" t="s">
+        <v>243</v>
       </c>
       <c r="N44" s="10" t="s">
-        <v>143</v>
+        <v>247</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="16" x14ac:dyDescent="0.35">
@@ -3171,20 +3165,20 @@
       <c r="I45" t="s">
         <v>147</v>
       </c>
-      <c r="K45" s="10" t="s">
+      <c r="K45" s="14" t="s">
         <v>162</v>
       </c>
       <c r="L45" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M45" s="13" t="s">
-        <v>245</v>
+      <c r="M45" s="12" t="s">
+        <v>243</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" ht="290" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>126</v>
       </c>
@@ -3212,17 +3206,17 @@
       <c r="I46" t="s">
         <v>146</v>
       </c>
-      <c r="K46" s="12" t="s">
-        <v>218</v>
+      <c r="K46" s="14" t="s">
+        <v>216</v>
       </c>
       <c r="L46" s="7">
         <v>46183</v>
       </c>
-      <c r="M46" s="13" t="s">
-        <v>241</v>
+      <c r="M46" s="12" t="s">
+        <v>239</v>
       </c>
       <c r="N46" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="16" x14ac:dyDescent="0.35">
@@ -3253,20 +3247,20 @@
       <c r="I47" t="s">
         <v>147</v>
       </c>
-      <c r="K47" s="10" t="s">
+      <c r="K47" s="14" t="s">
         <v>163</v>
       </c>
       <c r="L47" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M47" s="13" t="s">
-        <v>246</v>
+      <c r="M47" s="12" t="s">
+        <v>244</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="409.5" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>128</v>
       </c>
@@ -3294,20 +3288,20 @@
       <c r="I48" t="s">
         <v>146</v>
       </c>
-      <c r="K48" s="12" t="s">
-        <v>219</v>
+      <c r="K48" s="14" t="s">
+        <v>217</v>
       </c>
       <c r="L48" s="7">
         <v>46188</v>
       </c>
-      <c r="M48" s="13" t="s">
-        <v>226</v>
+      <c r="M48" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="N48" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" ht="290" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>81</v>
       </c>
@@ -3335,14 +3329,14 @@
       <c r="I49" t="s">
         <v>146</v>
       </c>
-      <c r="K49" s="12" t="s">
-        <v>220</v>
+      <c r="K49" s="14" t="s">
+        <v>218</v>
       </c>
       <c r="L49" s="7">
         <v>46176</v>
       </c>
-      <c r="M49" s="13" t="s">
-        <v>230</v>
+      <c r="M49" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="N49" s="10" t="s">
         <v>144</v>
@@ -3376,17 +3370,17 @@
       <c r="I50" t="s">
         <v>146</v>
       </c>
-      <c r="K50" s="10" t="s">
+      <c r="K50" s="14" t="s">
         <v>191</v>
       </c>
       <c r="L50" s="7">
         <v>46188</v>
       </c>
-      <c r="M50" s="13" t="s">
-        <v>230</v>
+      <c r="M50" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="N50" s="10" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="16" x14ac:dyDescent="0.35">
@@ -3417,20 +3411,20 @@
       <c r="I51" t="s">
         <v>146</v>
       </c>
-      <c r="K51" s="10" t="s">
+      <c r="K51" s="14" t="s">
         <v>192</v>
       </c>
       <c r="L51" s="7">
         <v>46185</v>
       </c>
-      <c r="M51" s="13" t="s">
-        <v>226</v>
+      <c r="M51" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" ht="116" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>131</v>
       </c>
@@ -3458,14 +3452,14 @@
       <c r="I52" t="s">
         <v>146</v>
       </c>
-      <c r="K52" s="12" t="s">
+      <c r="K52" s="14" t="s">
         <v>173</v>
       </c>
       <c r="L52" s="7">
         <v>46188</v>
       </c>
-      <c r="M52" s="13" t="s">
-        <v>230</v>
+      <c r="M52" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="N52" s="10" t="s">
         <v>177</v>
@@ -3499,14 +3493,14 @@
       <c r="I53" t="s">
         <v>146</v>
       </c>
-      <c r="K53" s="10" t="s">
+      <c r="K53" s="14" t="s">
         <v>164</v>
       </c>
       <c r="L53" s="7">
         <v>46234</v>
       </c>
-      <c r="M53" s="13" t="s">
-        <v>230</v>
+      <c r="M53" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="N53" s="10" t="s">
         <v>142</v>
@@ -3540,14 +3534,14 @@
       <c r="I54" t="s">
         <v>148</v>
       </c>
-      <c r="K54" s="10" t="s">
+      <c r="K54" s="14" t="s">
         <v>193</v>
       </c>
       <c r="L54" s="7">
         <v>46248</v>
       </c>
-      <c r="M54" s="13" t="s">
-        <v>247</v>
+      <c r="M54" s="12" t="s">
+        <v>245</v>
       </c>
       <c r="N54" s="10" t="s">
         <v>142</v>
@@ -3581,14 +3575,14 @@
       <c r="I55" t="s">
         <v>148</v>
       </c>
-      <c r="K55" s="10" t="s">
+      <c r="K55" s="14" t="s">
         <v>194</v>
       </c>
       <c r="L55" s="7">
         <v>46197</v>
       </c>
-      <c r="M55" s="13" t="s">
-        <v>231</v>
+      <c r="M55" s="12" t="s">
+        <v>229</v>
       </c>
       <c r="N55" s="10" t="s">
         <v>142</v>
@@ -3622,20 +3616,20 @@
       <c r="I56" t="s">
         <v>146</v>
       </c>
-      <c r="K56" s="10" t="s">
+      <c r="K56" s="14" t="s">
         <v>195</v>
       </c>
       <c r="L56" s="7">
         <v>46209</v>
       </c>
-      <c r="M56" s="13" t="s">
-        <v>226</v>
+      <c r="M56" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="N56" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>136</v>
       </c>
@@ -3663,17 +3657,17 @@
       <c r="I57" t="s">
         <v>148</v>
       </c>
-      <c r="K57" s="12" t="s">
+      <c r="K57" s="14" t="s">
         <v>174</v>
       </c>
       <c r="L57" s="7">
         <v>46204</v>
       </c>
-      <c r="M57" s="13" t="s">
-        <v>230</v>
+      <c r="M57" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="16" x14ac:dyDescent="0.35">
@@ -3704,14 +3698,14 @@
       <c r="I58" t="s">
         <v>146</v>
       </c>
-      <c r="K58" s="10" t="s">
+      <c r="K58" s="14" t="s">
         <v>165</v>
       </c>
       <c r="L58" s="7">
         <v>46188</v>
       </c>
-      <c r="M58" s="13" t="s">
-        <v>241</v>
+      <c r="M58" s="12" t="s">
+        <v>239</v>
       </c>
       <c r="N58" s="10" t="s">
         <v>177</v>
@@ -3745,20 +3739,20 @@
       <c r="I59" t="s">
         <v>146</v>
       </c>
-      <c r="K59" s="10" t="s">
+      <c r="K59" s="14" t="s">
         <v>166</v>
       </c>
       <c r="L59" s="7">
         <v>46178</v>
       </c>
-      <c r="M59" s="13" t="s">
-        <v>231</v>
+      <c r="M59" s="12" t="s">
+        <v>229</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>138</v>
       </c>
@@ -3786,20 +3780,20 @@
       <c r="I60" t="s">
         <v>146</v>
       </c>
-      <c r="K60" s="12" t="s">
+      <c r="K60" s="14" t="s">
         <v>175</v>
       </c>
       <c r="L60" s="8">
         <v>46188</v>
       </c>
-      <c r="M60" s="13" t="s">
-        <v>230</v>
+      <c r="M60" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="N60" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" ht="261" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="16" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>139</v>
       </c>
@@ -3827,17 +3821,17 @@
       <c r="I61" t="s">
         <v>146</v>
       </c>
-      <c r="K61" s="12" t="s">
-        <v>221</v>
+      <c r="K61" s="14" t="s">
+        <v>219</v>
       </c>
       <c r="L61" s="8">
         <v>46185</v>
       </c>
-      <c r="M61" s="13" t="s">
-        <v>226</v>
+      <c r="M61" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="16" x14ac:dyDescent="0.35">
@@ -3868,20 +3862,20 @@
       <c r="I62" t="s">
         <v>146</v>
       </c>
-      <c r="K62" s="10" t="s">
+      <c r="K62" s="14" t="s">
         <v>196</v>
       </c>
       <c r="L62" s="7">
         <v>46183</v>
       </c>
-      <c r="M62" s="13" t="s">
-        <v>245</v>
+      <c r="M62" s="12" t="s">
+        <v>243</v>
       </c>
       <c r="N62" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" ht="334" thickBot="1" x14ac:dyDescent="0.4">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
         <v>141</v>
       </c>
@@ -3909,17 +3903,17 @@
       <c r="I63" t="s">
         <v>146</v>
       </c>
-      <c r="K63" s="12" t="s">
-        <v>222</v>
+      <c r="K63" s="14" t="s">
+        <v>220</v>
       </c>
       <c r="L63" s="9">
         <v>46189</v>
       </c>
-      <c r="M63" s="13" t="s">
-        <v>248</v>
+      <c r="M63" s="12" t="s">
+        <v>246</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3950,59 +3944,24 @@
       <c r="I64" t="s">
         <v>146</v>
       </c>
-      <c r="K64" t="s">
+      <c r="K64" s="15" t="s">
         <v>197</v>
       </c>
       <c r="L64" s="11">
         <v>46215</v>
       </c>
-      <c r="M64" s="14" t="s">
-        <v>225</v>
+      <c r="M64" s="13" t="s">
+        <v>223</v>
       </c>
       <c r="N64" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" t="s">
-        <v>249</v>
-      </c>
-      <c r="B65" t="s">
-        <v>250</v>
-      </c>
-      <c r="C65" t="s">
-        <v>4</v>
-      </c>
-      <c r="D65" t="s">
-        <v>183</v>
-      </c>
-      <c r="E65" t="s">
-        <v>142</v>
-      </c>
-      <c r="F65" t="s">
-        <v>1</v>
-      </c>
-      <c r="G65" s="11">
-        <v>46204</v>
-      </c>
-      <c r="H65" s="11">
-        <v>46568</v>
-      </c>
-      <c r="I65" t="s">
-        <v>146</v>
-      </c>
-      <c r="K65" t="s">
-        <v>251</v>
-      </c>
-      <c r="L65" s="11">
-        <v>46215</v>
-      </c>
-      <c r="M65" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="N65" t="s">
-        <v>142</v>
-      </c>
+    <row r="65" spans="7:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
+      <c r="L65" s="11"/>
+      <c r="M65" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -4070,7 +4029,6 @@
     <hyperlink ref="M62" r:id="rId61" display="mailto:Bernardino.lagoa@claro.com.br" xr:uid="{5164CF39-CB99-46E2-98AB-6925F0CCED92}"/>
     <hyperlink ref="M63" r:id="rId62" display="mailto:Bernardino.lagoa@claro.com.br,Bruno.Feijo@claro.com.br" xr:uid="{4606E8EE-F97F-4D0A-A1E5-BA36AA180B25}"/>
     <hyperlink ref="M64" r:id="rId63" display="mailto:paulo.rocha@claro.com.br" xr:uid="{E0A00782-EA79-4CE3-94A7-F14E6B4CD6D9}"/>
-    <hyperlink ref="M65" r:id="rId64" display="mailto:paulo.rocha@claro.com.br" xr:uid="{25BB1CD6-87C3-4FE2-928F-94D7442F0426}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4086,6 +4044,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="48a4df2c-25c0-4bd5-9ad3-969cdc4eb0ad">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fe5609ce-cb92-4045-944c-c105fdf4b20b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006A0F678961C25F42A60818D832EED552" ma:contentTypeVersion="15" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="dc2a7ab8599bba470a78deafa62af16c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="48a4df2c-25c0-4bd5-9ad3-969cdc4eb0ad" xmlns:ns3="fe5609ce-cb92-4045-944c-c105fdf4b20b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ffd182497d787a9e927f0f89c1000013" ns2:_="" ns3:_="">
     <xsd:import namespace="48a4df2c-25c0-4bd5-9ad3-969cdc4eb0ad"/>
@@ -4320,17 +4289,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="48a4df2c-25c0-4bd5-9ad3-969cdc4eb0ad">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fe5609ce-cb92-4045-944c-c105fdf4b20b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{421192A4-7E63-4E34-BFD9-A0D092033413}">
   <ds:schemaRefs>
@@ -4340,6 +4298,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F58F0C4-7563-4480-B156-7EBAF344CD6A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="48a4df2c-25c0-4bd5-9ad3-969cdc4eb0ad"/>
+    <ds:schemaRef ds:uri="fe5609ce-cb92-4045-944c-c105fdf4b20b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4FC87EE-D01F-4F08-8D84-C3D05E1D5A3A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4356,15 +4325,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F58F0C4-7563-4480-B156-7EBAF344CD6A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="48a4df2c-25c0-4bd5-9ad3-969cdc4eb0ad"/>
-    <ds:schemaRef ds:uri="fe5609ce-cb92-4045-944c-c105fdf4b20b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Base Limpa.xlsx
+++ b/Base Limpa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corpclarobr-my.sharepoint.com/personal/bruno_mandarsilva_claro_com_br/Documents/Documentos/dashboard-logistica/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4725" documentId="8_{C973436A-53F7-4C3D-9821-DB0945EE825D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2872E00B-344B-4FBB-87D2-877A08003732}"/>
+  <xr:revisionPtr revIDLastSave="4754" documentId="8_{C973436A-53F7-4C3D-9821-DB0945EE825D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D302A5FF-793D-471C-A754-F4C7C3F27BB1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="254">
   <si>
     <t>Prioridade</t>
   </si>
@@ -530,13 +530,7 @@
     <t>Melhoria continua dos processos de Logística na nova Plataforma, eliminando os gaps e desenvolvendo soluções de melhoria para as operações.</t>
   </si>
   <si>
-    <t>Backlog - Tratar em Julho</t>
-  </si>
-  <si>
     <t>Em processo de criação de Centro Americel e CNPJ's para evidencia de de/para para auditoria, com a finalidade de evitar problemas de comprovação de migração do estoque.</t>
-  </si>
-  <si>
-    <t>1. Ampliação de áreas de Atedimento no RS - Em processo de captação , Adriana irá informar possibilidade de inicio na primeira semana de junho - Adriana poderá utilizar o estoque em mãos para iniciar, porém é necessário solicitar ao André ajuste do estoque.</t>
   </si>
   <si>
     <t>Report Finalizado.
@@ -556,19 +550,10 @@
 2. Entrega do Relatório - 22/05</t>
   </si>
   <si>
-    <t>1. Sera retomado os testes com drones em Campinas, em conjunto com a Marinalva.
-2. Inicio de uma pesquisa de mercado para avaliar soluções mais avançadas utilizadas no setor, devido ao material ainda não ser totalmente serializado.
-3. E retomar uma frente que já havia sido iniciada, relacionada ao uso de RFID, junto ao time de processos.</t>
-  </si>
-  <si>
     <t>1. Segue em validação da SOL na Torre de Controle.
 2. Treinamento / Workshop COPILOT para diretoria de Logística - 31/05</t>
   </si>
   <si>
-    <t>1.Relatório Paliativo enviado pela Mariana Mani em 25/05.
-2.Relatório definitivo previsto para iniciar testes na segunda quinzena de Junho (José Rodrigo e Fábio)</t>
-  </si>
-  <si>
     <t>1. Dado o baixo risco, ficará em Backlog até 24/05
 2. Validar a retomada do assunto em 26/05.</t>
   </si>
@@ -601,33 +586,15 @@
     <t>DGP / RAI – Estratégico</t>
   </si>
   <si>
-    <t>Apuração MAI/26 27 PAS</t>
-  </si>
-  <si>
-    <t>Necessário Revisar o FCST, Projeto realizando abaixo do FCST</t>
-  </si>
-  <si>
     <t>29/05 - Alinhamento com Time McKinsey para avaliação de dados e geração cronograma .10/06 BID Transportes ainda em etapa de planejamento com apoio da consultoria McKinsey</t>
   </si>
   <si>
     <t>Incoorporado no LOG-07</t>
   </si>
   <si>
-    <t>1. A estrutura do PGP de Amplificadores foi finalizada, com todo o fluxo devidamente definido em conjunto com os times de Reparo e CD. O material segue agora para aprovação do time da Cléria, visando o avanço para homologação e posterior implementação prática do projeto.</t>
-  </si>
-  <si>
-    <t>Reunião marcada para sexta-feira (12/06) com a Catalde, com a finalidade de fechar o escopo para que eles possam precificar as customizações e definir os prazos para execução - 15/06</t>
-  </si>
-  <si>
     <t>Protótipo do sistema de controle de estoque direta e reversa para Epos. Em desenvolvimento pelo fornecedor TCIA, previsão para inicio do piloto na EPO ANTEC - SPI - para inicio da 1º quinzena de Junho. com visão inicial do controle da reversa - (Acessórios apontados pelos técnicos no TOA). em Andamento.</t>
   </si>
   <si>
-    <t>1. Realizar o entendimento da ferramenta dentro da operação atual da Claro, definindo se faz sentido a sua utilização. Definir a utilização da ferramenta, podendo ampliar o uso para tratar outras ocorrências caso haja necessidade - 15/06.</t>
-  </si>
-  <si>
-    <t>1. Lencione informou um possivel encerramento, checar e validar a informação - (22/05).10/06 BID SP, está pendente de subirmos uma base com os targets no Ariba, que deve acontecer ao longo do dia</t>
-  </si>
-  <si>
     <t>Demanda em Backlog, retomar o tema em agosto.</t>
   </si>
   <si>
@@ -641,11 +608,6 @@
   </si>
   <si>
     <t>Necessário apuração da SD com Pablo do Tributário</t>
-  </si>
-  <si>
-    <t>1. 10/06 - Avaliar com Dino se haverá ajuste de FCST
-2.01/06 - Apurado abaixo da meta
-3. Demanda atual com: 1030 pontos de coleta, 258 lojas próprias e 772 agentes autorizados.</t>
   </si>
   <si>
     <t>Apuração MAIO - pendente RAQUEL e HIDEKI;
@@ -688,29 +650,9 @@
 FCST parcial. O Escopo contempla Retorno de fontes porém Controle está com racional em andamento</t>
   </si>
   <si>
-    <t>1. Foi feita todas as apresentações de relatórios, testes etc, e foram apresentadas para o Demis, a conclusão até o momento foi que seria necessario novos parâmetros , novos estudos para mais eficácia do processo.
-2. Jackson e Mauricio vão alinhar as novas fases e distribuição de tarefas, para nos retornar com os prazos em relação ao estudo que ira iniciar.</t>
-  </si>
-  <si>
     <t>1. Revisão do FCST para a próxima reunião, mostrando plano de ação para redução - 28/07
 2. PR em estudo e RS Finalizado (30/05) - Pendente de verba para pagamento.
 3. Próximos passos: SPI, Centro Oeste, Norte e Nordeste - programado para 2027, sem verba.</t>
-  </si>
-  <si>
-    <t>Enviado e-mail na data de hoje 08/06/2026 para os transportadores efetuarem as rotas. Prazo para resposta do transportador: 11/06/2026
-Prazo final de analises: 26/06/2026. Responsável: Leandro / Thiago</t>
-  </si>
-  <si>
-    <t>1. iniciamos a análise e validação junto à SIC – Segurança Lógica Corporativa, que trouxe considerações positivas sobre a forma como estruturamos o projeto.
-2. Entrevista com todas as coordenações (finaliza em 07/08)</t>
-  </si>
-  <si>
-    <t>1. 08/06 - Reunião com Marcia PGR para alinhamento de seguimento com TEX
-2. 10/06 - alinahmento da Especificação funcional Catalde x TEX
-1. RHOMEGA não qualificada, Vencedora TEX (preço competitivo). Proximo passo visita a base da TEX a pedido de gerenciamento de RISCO. Mesa de negociação após etapa de gerenciamento de RISCO. Estratégia de RAMPUP (SUL e SUDESTE).
-2. 22/05 - CW278234, alinhado com area de risco disussão de minuta para andarmos na paralela (analise juridico/risco).
-3. Reunião com a TEX semanal para alinhamento tecnico - Pendencia de envio de-para de ocorrência e criar grupo com o pessoal da tex e catalde para simplificar as demandas. 
-04. 09/06 reunião com a Tex EM 10/06  para alinhamento sobre modalidade de seguro: Cross doc vs. base do fornecedor -  10/06 Compras fazer validação da aderência do fornecedor ao modelo (cross-docking e pós) , GR trarão alternativas de modelos de seguro disponíveis, além da proposta atual.</t>
   </si>
   <si>
     <t>1. Ingrid informou que ira atualizar o Planner com todos seus projetos.
@@ -741,16 +683,159 @@
 Jun/26: Análise de redução de custo com a não baixa dos insumos.</t>
   </si>
   <si>
-    <t>1. Ambientação do Septeto - 01/06 a 12/06.
-2. Início da Operação Assistida - 15/06 a 30/06.</t>
-  </si>
-  <si>
     <t>1. O setor necessita receber, via API, as informações referentes aos pagamentos de impostos realizados à Receita Federal. Demanda já foi apresentada ao time de Analytics, porém, até o momento, não houve avanços (22/05).
 2. aguardando e-mail da Michele com o escopo da demanda, para dar seguimento com os setores necessarios (29/05).
 08/06 - Solicitado atualização e detalhes do projeto para a Ingrid.</t>
   </si>
   <si>
-    <t>15/06 - Análise da volumetria e memorial descritivo
+    <t>Diego.RochaSantos@claro.com.br</t>
+  </si>
+  <si>
+    <t>Ismael.Martins@claro.com.br</t>
+  </si>
+  <si>
+    <t>paulo.rocha@claro.com.br</t>
+  </si>
+  <si>
+    <t>alex.lencione@claro.com.br</t>
+  </si>
+  <si>
+    <t>gustavo.mendes@claro.com.br</t>
+  </si>
+  <si>
+    <t>Santos.PBruno@claro.com.br</t>
+  </si>
+  <si>
+    <t>Marcelo.Saleme@claro.com.br</t>
+  </si>
+  <si>
+    <t>helder.ssilva@claro.com.br</t>
+  </si>
+  <si>
+    <t>fabio.ocosta@claro.com.br</t>
+  </si>
+  <si>
+    <t>evandro.moratori@claro.com.br</t>
+  </si>
+  <si>
+    <t>ADEMILSON.SILVA@claro.com.br</t>
+  </si>
+  <si>
+    <t>leandro.carlos@claro.com.br</t>
+  </si>
+  <si>
+    <t>Jefferson.Santana@claro.com.br</t>
+  </si>
+  <si>
+    <t>Marileia.Passos@claro.com.br</t>
+  </si>
+  <si>
+    <t>fabiana.pons@claro.com.br</t>
+  </si>
+  <si>
+    <t>jeferson.teixeira@claro.com.br</t>
+  </si>
+  <si>
+    <t>Fabio.Lima@claro.com.br</t>
+  </si>
+  <si>
+    <t>cleria.plaster@claro.com.br</t>
+  </si>
+  <si>
+    <t>ingrid.alcici@claro.com.br</t>
+  </si>
+  <si>
+    <t>Ildo.Lima@claro.com.br</t>
+  </si>
+  <si>
+    <t>LUCAS.RIBEIRO@claro.com.br</t>
+  </si>
+  <si>
+    <t>Bernardino.lagoa@claro.com.br</t>
+  </si>
+  <si>
+    <t>marcelo.paulino@claro.com.br</t>
+  </si>
+  <si>
+    <t>fabricio.friolani@claro.com.br</t>
+  </si>
+  <si>
+    <t>SEM AÇÃO</t>
+  </si>
+  <si>
+    <t>30/06 - Estruturação da Calendarização Atual e Pontos de Melhorias e Impactos
+30/08 - Mapeamento da Capilaridade
+20/12 - Levantamento do retorno das aplicadas x retorno das melhorias</t>
+  </si>
+  <si>
+    <t>06/08 - Definir quais projetos serão executados e o cronograma de implantação
+13/08 - Apresentação do cronograma de atividades para 2026 pela Accenture
+21/08 - Definir premissas dos estudos
+31/12 - Acompanhar a implantação e demonstrar os ganhos.</t>
+  </si>
+  <si>
+    <t>LOG-64</t>
+  </si>
+  <si>
+    <t>Rastreabilidade - COMEX</t>
+  </si>
+  <si>
+    <t>Apuração MAI/26 27 PAS - Projeto finalizando em acompanhamento de report financeiro</t>
+  </si>
+  <si>
+    <t>Necessário Revisar o FCST, Projeto realizando abaixo do FCST - Em avaliação com Edgar para avaliar o 4º mês reunião - Pendente reunião de alinhamento até 19/06</t>
+  </si>
+  <si>
+    <t>23/06/2026 - Escopo de métricas de consulta da jornada dos terminais para Scrap por rotatividade.</t>
+  </si>
+  <si>
+    <t>30/06/26 - Ajustes e Finalização do PGP " Sobra de Material, com a liberação tributaria;</t>
+  </si>
+  <si>
+    <t>A Cléria informa que não tem definição sequencial, ou sequenciada do escopo do Projeto, sinalizou que precisa de definições gerencias para seguir com o mesmo. Permanecera em backlog, ate segunda ordem.</t>
+  </si>
+  <si>
+    <t>19/06 - Detalhamento da solução para precificação pela Catalde e OPLs</t>
+  </si>
+  <si>
+    <t>1. Início da Operação Assistida - 15/06 a 30/06.</t>
+  </si>
+  <si>
+    <t>1. Lencione informou um possivel encerramento, checar e validar a informação - (22/05).10/06 BID SP, está pendente de subirmos uma base com os targets no Ariba- Enviado para compras em 12/06 SR2168673643</t>
+  </si>
+  <si>
+    <t>Demanda encerrada.</t>
+  </si>
+  <si>
+    <t>1. 10/06 - Avaliar com Dino se haverá ajuste de FCST
+2.01/06 - Apurado abaixo da meta
+3. Demanda atual com: 1030 pontos de coleta, 258 lojas próprias e 772 agentes autorizados. Ação: Aumento do número de lojas Campanhas de incentivo para o cliente fazer devolução na loja,campanha para clientes de 8º base</t>
+  </si>
+  <si>
+    <t>Enviado e-mail (08/06) para os transportadores efetuarem as rotas. Prazo para resposta do transportador: 11/06/2026
+Prazo final de analises: 26/06/2026. Responsável: Leandro / Thiago</t>
+  </si>
+  <si>
+    <t>1. iniciamos a análise e validação junto à SIC – Segurança Lógica Corporativa, que trouxe considerações positivas sobre a forma como estruturamos o projeto.
+2. Entrevista com todas as coordenações (finaliza em 07/08) - acompanhamento semanal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 08/06 - Reunião com Marcia PGR para alinhamento de seguimento com TEX
+2. 10/06 - alinahmento da Especificação funcional Catalde x TEX
+1. RHOMEGA não qualificada, Vencedora TEX (preço competitivo). Proximo passo visita a base da TEX a pedido de gerenciamento de RISCO. Mesa de negociação após etapa de gerenciamento de RISCO. Estratégia de RAMPUP (SUL e SUDESTE).
+2. 22/05 - CW278234, alinhado com area de risco disussão de minuta para andarmos na paralela (analise juridico/risco).
+3. Reunião com a TEX semanal para alinhamento tecnico - Pendencia de envio de-para de ocorrência e criar grupo com o pessoal da tex e catalde para simplificar as demandas. 
+04. 09/06 reunião com a Tex EM 10/06  para alinhamento sobre modalidade de seguro: Cross doc vs. base do fornecedor -  10/06 Compras fazer validação da aderência do fornecedor ao modelo (cross-docking e pós) , GR trarão alternativas de modelos de seguro disponíveis, além da proposta atual. (Agenda para 16/06)
+15/06 As especificações técnicas foram validadas pela TEX. Renan (TEX) irá abrir a demanda para desenvolvimento do endpoint, com prazo estimado de 20 a 30 dias.
+Direcionamentos da reunião de 16/06 com GR foi definido as seguintes ações a serem concluídas pela logística: - Avaliar manual de sinistro enviado pela transportadora.
+- Avaliar veículo previsto para operação (carro de passeio).
+- Apresentar minuta do contrato Claro ao prestador.
+- Validar com o transportador a aderência ao modelo da Claro.
+- Agendar nova reunião com GR após as definições para continuidade dos próximos passos.
+</t>
+  </si>
+  <si>
+    <t>19/06 - Análise da volumetria e separação em 2 arquivos (SC/RS e RS/Rs) e memorial descritivo (Jaime / Quinete)
 15/06 - Marileia levantará porta pallet para dimensionar espaço (faturamento mensal para ver se consigo transformar Pp)
 26/05 - Protege (Erick Viana) vai fazer estudo no SUL. Lencione vai levantar volumetria do SUL
 1. Estudo mezo região
@@ -759,115 +844,59 @@
 3.1 Avaliar com Regional Repeto a divisão comercial da regional que se divide em "capital" e "interior").
 4. Paralelo define a abertura das regionais
 5. BID: Abrir considerando os 2 cenários
-5.1 Quebra Mezo região os volumes</t>
-  </si>
-  <si>
-    <t>1. Implementação da regra no sistema, efetuando os testes com a nova regra - 03/06.
+5.1 Quebra Mezo região os volumes
+16/06 Fabricio solicitou abertura de BID separado , Jaime vai levantar base para precificação com separação dos volume de Norte e Sul/Precificação separadas prazo 19/06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Implementação da regra no sistema, efetuando os testes com a nova regra - 03/06.
 2. Minuta estava em validação em Compras e com a Márcia (PGR)... retornei agora para o jurídico... após isso vai para a TEX
-porém, temos um item pendente: se a TEX vai ou não aderir ao nosso programa de seguros e, pelo que entendi com a Márcia, essa definição depende de uma reunião que precisa ocorrer entre ela e o Fabrício</t>
-  </si>
-  <si>
-    <t>10/06 - Magali devolverá revisão do cronograma.
-12/06 - Trazer time de PGR (Márcia) para as proximas agendas,Consultoria McKinsey está realizando agendas periódicas conosco, a próxima agenda de trabalho será no dia 12/06
-Levantamento de dados para consultoria, retornar FUP com Lencione - 05/06 .Reunião em 09/06</t>
+porém, temos um item pendente: se a TEX vai ou não aderir ao nosso programa de seguros e, pelo que entendi com a Márcia, essa definição depende de uma reunião que precisa ocorrer entre ela e o Fabrício
+12/06 - Estamos com reunião recorrente.
+3 transportadores ajustados, monitorando com eles até final do mês 30/06.
+Pendencia soltar comunicado executivo que esta pendente com o Helder e Fabricio. 
+18/06 - Comparando tabela do Frete Minimo x Fracionado
+19/06 - Relatório de analise </t>
+  </si>
+  <si>
+    <t>1. Realizar o entendimento da ferramenta dentro da operação atual da Claro, definindo se faz sentido a sua utilização. Definir a utilização da ferramenta, podendo ampliar o uso para tratar outras ocorrências caso haja necessidade.
+2. Reunião entre coordenação e gerencia de transportes para alianhar o tema.</t>
+  </si>
+  <si>
+    <t>1.Relatório definitivo previsto para iniciar testes na segunda quinzena de Junho (José Rodrigo e Fábio). Alinhameento homologação 16/06
+2.Relatório Paliativo enviado pela Mariana Mani em 25/05.
+3. Reuniões recorrentes para mensurar os entregaveis, relatporio definitivo pendente recebimento de algumas informaçoes das areas envolvidas, vamos considerar inicio da homologação até final de junho.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Ampliação de áreas de Atedimento no RS - 5 Cidades. ( Gravatai, Canoas,Cachoerinha, Vanon e Alvorada) 15/06. 
+Estruturar uma avaliação com maior frequência. Por ex Unificar regiões. Fabricio solicitou que seja feito o acompanhamento. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TO DO para até 16/06
+1. de/para de veiculo (Claro) - concluído
+2. tabela da TEX (CLARO)
+3. Divisão das motos para atendimento (CLARO)
+4. Abrir Engenharia / Movel (Mackinsey)
+5. Abrir base 25 com custos extras da móvel e reunião para entendimento da base (Jaime vai entregar até dia 18/06)
+6. Prazo: Magali necessita revisar prazo de compras </t>
   </si>
   <si>
     <t>1. Necessário atualizar ação pós Piloto
 1. Piloto em Guarulhos realizado e finalizado em 25/05
 2. Reunião de apuração de resultados para 28/05, apos reunião apresentar resultados.
-3.Foi realizada a reunião de fechamento da apresentação do piloto de Guarulhos. Próximo passo: será programada, ainda neste mês, a agenda com o Edgar para apresentação dos resultados e alinhamento dos próximos direcionamentos. Previsão até 17/06.</t>
-  </si>
-  <si>
-    <t>Diego.RochaSantos@claro.com.br</t>
-  </si>
-  <si>
-    <t>Ismael.Martins@claro.com.br</t>
-  </si>
-  <si>
-    <t>paulo.rocha@claro.com.br</t>
-  </si>
-  <si>
-    <t>alex.lencione@claro.com.br</t>
-  </si>
-  <si>
-    <t>gustavo.mendes@claro.com.br</t>
-  </si>
-  <si>
-    <t>Santos.PBruno@claro.com.br</t>
-  </si>
-  <si>
-    <t>Marcelo.Saleme@claro.com.br</t>
-  </si>
-  <si>
-    <t>helder.ssilva@claro.com.br</t>
-  </si>
-  <si>
-    <t>fabio.ocosta@claro.com.br</t>
-  </si>
-  <si>
-    <t>evandro.moratori@claro.com.br</t>
-  </si>
-  <si>
-    <t>ADEMILSON.SILVA@claro.com.br</t>
-  </si>
-  <si>
-    <t>leandro.carlos@claro.com.br</t>
-  </si>
-  <si>
-    <t>Jefferson.Santana@claro.com.br</t>
-  </si>
-  <si>
-    <t>Marileia.Passos@claro.com.br</t>
-  </si>
-  <si>
-    <t>fabiana.pons@claro.com.br</t>
-  </si>
-  <si>
-    <t>jeferson.teixeira@claro.com.br</t>
-  </si>
-  <si>
-    <t>Fabio.Lima@claro.com.br</t>
-  </si>
-  <si>
-    <t>cleria.plaster@claro.com.br</t>
-  </si>
-  <si>
-    <t>ingrid.alcici@claro.com.br</t>
-  </si>
-  <si>
-    <t>Marinalva.Marculino@claro.com.br;</t>
-  </si>
-  <si>
-    <t>Ildo.Lima@claro.com.br</t>
-  </si>
-  <si>
-    <t>LUCAS.RIBEIRO@claro.com.br</t>
-  </si>
-  <si>
-    <t>Bernardino.lagoa@claro.com.br</t>
-  </si>
-  <si>
-    <t>marcelo.paulino@claro.com.br</t>
-  </si>
-  <si>
-    <t>fabricio.friolani@claro.com.br</t>
-  </si>
-  <si>
-    <t>Bernardino.lagoa@claro.com.br,Bruno.Feijo@claro.com.br</t>
-  </si>
-  <si>
-    <t>SEM AÇÃO</t>
-  </si>
-  <si>
-    <t>30/06 - Estruturação da Calendarização Atual e Pontos de Melhorias e Impactos
-30/08 - Mapeamento da Capilaridade
-20/12 - Levantamento do retorno das aplicadas x retorno das melhorias</t>
-  </si>
-  <si>
-    <t>06/08 - Definir quais projetos serão executados e o cronograma de implantação
-13/08 - Apresentação do cronograma de atividades para 2026 pela Accenture
-21/08 - Definir premissas dos estudos
-31/12 - Acompanhar a implantação e demonstrar os ganhos.</t>
+3.Foi realizada a reunião de fechamento da apresentação do piloto de Guarulhos. Próximo passo: será programada, ainda neste mês, a agenda com o Edgar para apresentação dos resultados e alinhamento dos próximos direcionamentos. Previsão até 17/06.Novo piloto com novo parceiro em Guarulhos a definir data</t>
+  </si>
+  <si>
+    <t>Reunião de alimento para entendimento do processo planejamento das ações iniciais 11/06/2026 ok
+Agenda recorrente (diária) de trabalho para mapeamento do processo atual</t>
+  </si>
+  <si>
+    <t>Marinalva.Marculino@claro.com.br</t>
+  </si>
+  <si>
+    <t>Bruno.Feijo@claro.com.br</t>
+  </si>
+  <si>
+    <t>michelle.rodrigues@claro.com.br</t>
   </si>
 </sst>
 </file>
@@ -963,7 +992,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -983,25 +1012,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hiperlink" xfId="3" builtinId="8"/>
@@ -1338,7 +1357,7 @@
         <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C1" t="s">
         <v>10</v>
@@ -1368,29 +1387,29 @@
         <v>151</v>
       </c>
       <c r="M1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="N1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E2" t="s">
-        <v>177</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="D2" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G2" s="1">
@@ -1399,39 +1418,39 @@
       <c r="H2" s="1">
         <v>46204</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K2" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="L2" s="7">
+      <c r="K2" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="L2" s="1">
         <v>46203</v>
       </c>
-      <c r="M2" s="12" t="s">
-        <v>221</v>
+      <c r="M2" s="7" t="s">
+        <v>201</v>
       </c>
       <c r="N2" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E3" t="s">
-        <v>142</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="D3" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G3" s="2">
@@ -1440,39 +1459,39 @@
       <c r="H3" s="2">
         <v>46357</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K3" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="L3" s="7">
-        <v>46184</v>
-      </c>
-      <c r="M3" s="12" t="s">
-        <v>222</v>
+      <c r="K3" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="L3" s="1">
+        <v>46196</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>202</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="D4" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G4" s="1">
@@ -1481,39 +1500,39 @@
       <c r="H4" s="1">
         <v>46357</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K4" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="L4" s="7">
-        <v>46185</v>
-      </c>
-      <c r="M4" s="12" t="s">
-        <v>223</v>
+      <c r="K4" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="L4" s="1">
+        <v>46199</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
-        <v>183</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D5" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G5" s="2">
@@ -1522,39 +1541,39 @@
       <c r="H5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="K5" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="L5" s="7" t="s">
+      <c r="K5" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="12" t="s">
-        <v>224</v>
+      <c r="M5" s="7" t="s">
+        <v>204</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E6" t="s">
-        <v>142</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="D6" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G6" s="1">
@@ -1563,39 +1582,39 @@
       <c r="H6" s="1">
         <v>46357</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K6" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="L6" s="7">
+      <c r="K6" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="L6" s="1">
         <v>46193</v>
       </c>
-      <c r="M6" s="12" t="s">
-        <v>225</v>
+      <c r="M6" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D7" t="s">
-        <v>183</v>
-      </c>
-      <c r="E7" t="s">
-        <v>142</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="D7" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G7" s="2">
@@ -1604,39 +1623,39 @@
       <c r="H7" s="2">
         <v>46473</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K7" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="L7" s="7">
-        <v>46183</v>
-      </c>
-      <c r="M7" s="12" t="s">
-        <v>226</v>
+      <c r="K7" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="L7" s="1">
+        <v>46192</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>206</v>
       </c>
       <c r="N7" s="10" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C8" t="s">
-        <v>182</v>
-      </c>
-      <c r="D8" t="s">
-        <v>183</v>
-      </c>
-      <c r="E8" t="s">
-        <v>142</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="C8" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G8" s="1">
@@ -1645,39 +1664,39 @@
       <c r="H8" s="1">
         <v>46387</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K8" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="L8" s="7">
+      <c r="K8" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="L8" s="1">
         <v>46204</v>
       </c>
-      <c r="M8" s="12" t="s">
-        <v>227</v>
+      <c r="M8" s="7" t="s">
+        <v>207</v>
       </c>
       <c r="N8" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="9" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D9" t="s">
-        <v>183</v>
-      </c>
-      <c r="E9" t="s">
-        <v>142</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="D9" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G9" s="2">
@@ -1686,39 +1705,39 @@
       <c r="H9" s="2">
         <v>46357</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K9" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="L9" s="7">
+      <c r="K9" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="L9" s="1">
         <v>46183</v>
       </c>
-      <c r="M9" s="12" t="s">
-        <v>228</v>
+      <c r="M9" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="N9" s="10" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="10" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D10" t="s">
-        <v>183</v>
-      </c>
-      <c r="E10" t="s">
-        <v>142</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="D10" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G10" s="1">
@@ -1727,39 +1746,39 @@
       <c r="H10" s="1">
         <v>46564</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K10" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="L10" s="7">
+      <c r="K10" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="L10" s="1">
         <v>46189</v>
       </c>
-      <c r="M10" s="12" t="s">
-        <v>229</v>
+      <c r="M10" s="7" t="s">
+        <v>209</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D11" t="s">
-        <v>183</v>
-      </c>
-      <c r="E11" t="s">
-        <v>142</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="D11" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G11" s="2">
@@ -1768,39 +1787,39 @@
       <c r="H11" s="2">
         <v>46564</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K11" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="L11" s="7">
+      <c r="K11" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="L11" s="1">
         <v>46185</v>
       </c>
-      <c r="M11" s="12" t="s">
-        <v>224</v>
+      <c r="M11" s="7" t="s">
+        <v>204</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D12" t="s">
-        <v>183</v>
-      </c>
-      <c r="E12" t="s">
-        <v>142</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="D12" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G12" s="1">
@@ -1809,39 +1828,39 @@
       <c r="H12" s="1">
         <v>46387</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K12" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="L12" s="7">
+      <c r="K12" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="L12" s="1">
         <v>46185</v>
       </c>
-      <c r="M12" s="12" t="s">
-        <v>230</v>
+      <c r="M12" s="7" t="s">
+        <v>210</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C13" t="s">
-        <v>182</v>
-      </c>
-      <c r="D13" t="s">
-        <v>183</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="C13" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G13" s="2">
@@ -1850,39 +1869,39 @@
       <c r="H13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="L13" s="7" t="s">
+      <c r="L13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M13" s="12" t="s">
-        <v>231</v>
+      <c r="M13" s="7" t="s">
+        <v>211</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E14" t="s">
-        <v>142</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="E14" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G14" s="1">
@@ -1891,39 +1910,39 @@
       <c r="H14" s="1">
         <v>46357</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="K14" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="L14" s="7">
-        <v>46188</v>
-      </c>
-      <c r="M14" s="12" t="s">
-        <v>230</v>
+      <c r="K14" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="L14" s="1">
+        <v>46196</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>210</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E15" t="s">
-        <v>142</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="E15" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G15" s="2">
@@ -1932,39 +1951,39 @@
       <c r="H15" s="2">
         <v>46357</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K15" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="L15" s="7">
+      <c r="K15" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="L15" s="1">
         <v>46231</v>
       </c>
-      <c r="M15" s="12" t="s">
-        <v>225</v>
+      <c r="M15" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="N15" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    <row r="16" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A16" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E16" t="s">
-        <v>142</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="E16" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F16" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G16" s="1">
@@ -1973,39 +1992,39 @@
       <c r="H16" s="1">
         <v>46387</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K16" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="L16" s="7">
+      <c r="K16" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="L16" s="1">
         <v>46199</v>
       </c>
-      <c r="M16" s="12" t="s">
-        <v>232</v>
+      <c r="M16" s="7" t="s">
+        <v>212</v>
       </c>
       <c r="N16" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C17" t="s">
-        <v>182</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="C17" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E17" t="s">
-        <v>142</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="E17" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G17" s="2">
@@ -2014,39 +2033,39 @@
       <c r="H17" s="2">
         <v>46387</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="K17" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="L17" s="7">
+      <c r="K17" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="L17" s="1">
         <v>46203</v>
       </c>
-      <c r="M17" s="12" t="s">
-        <v>233</v>
+      <c r="M17" s="7" t="s">
+        <v>213</v>
       </c>
       <c r="N17" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+    <row r="18" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E18" t="s">
-        <v>142</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="E18" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G18" s="1">
@@ -2055,39 +2074,39 @@
       <c r="H18" s="1">
         <v>46357</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="K18" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="L18" s="7">
+      <c r="K18" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="L18" s="1">
         <v>46209</v>
       </c>
-      <c r="M18" s="12" t="s">
-        <v>234</v>
+      <c r="M18" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="N18" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="19" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C19" t="s">
-        <v>182</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="C19" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E19" t="s">
-        <v>142</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="E19" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G19" s="2">
@@ -2096,39 +2115,39 @@
       <c r="H19" s="2">
         <v>46357</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="K19" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="L19" s="7" t="s">
+      <c r="K19" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M19" s="12" t="s">
-        <v>235</v>
+      <c r="M19" s="7" t="s">
+        <v>215</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E20" t="s">
-        <v>142</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="E20" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F20" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G20" s="1">
@@ -2137,39 +2156,39 @@
       <c r="H20" s="1">
         <v>46387</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K20" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="L20" s="7">
-        <v>46188</v>
-      </c>
-      <c r="M20" s="12" t="s">
-        <v>236</v>
+      <c r="K20" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="L20" s="1">
+        <v>46203</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>216</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A21" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E21" t="s">
-        <v>142</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="E21" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F21" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G21" s="2">
@@ -2178,39 +2197,39 @@
       <c r="H21" s="2">
         <v>46387</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K21" s="14" t="s">
+      <c r="K21" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="L21" s="7">
+      <c r="L21" s="1">
         <v>46188</v>
       </c>
-      <c r="M21" s="12" t="s">
-        <v>237</v>
+      <c r="M21" s="7" t="s">
+        <v>217</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A22" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E22" t="s">
-        <v>142</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="E22" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F22" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G22" s="1">
@@ -2219,39 +2238,39 @@
       <c r="H22" s="1">
         <v>46387</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="K22" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="L22" s="7">
-        <v>46188</v>
-      </c>
-      <c r="M22" s="12" t="s">
-        <v>238</v>
+      <c r="K22" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="L22" s="1">
+        <v>46196</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A23" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E23" t="s">
-        <v>142</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="E23" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G23" s="2">
@@ -2260,39 +2279,39 @@
       <c r="H23" s="2">
         <v>46387</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="K23" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="L23" s="7">
-        <v>46189</v>
-      </c>
-      <c r="M23" s="12" t="s">
-        <v>224</v>
+      <c r="K23" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="L23" s="1">
+        <v>46192</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>204</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A24" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G24" s="1">
@@ -2301,39 +2320,39 @@
       <c r="H24" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="K24" s="14" t="s">
+      <c r="K24" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="L24" s="7" t="s">
+      <c r="L24" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M24" s="12" t="s">
-        <v>224</v>
+      <c r="M24" s="7" t="s">
+        <v>204</v>
       </c>
       <c r="N24" s="10" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A25" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G25" s="2">
@@ -2342,39 +2361,39 @@
       <c r="H25" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="K25" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="L25" s="7" t="s">
+      <c r="K25" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M25" s="12" t="s">
-        <v>229</v>
+      <c r="M25" s="7" t="s">
+        <v>209</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A26" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D26" t="s">
-        <v>183</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="D26" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E26" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G26" s="1">
@@ -2383,39 +2402,39 @@
       <c r="H26" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="K26" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="L26" s="7" t="s">
+      <c r="K26" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M26" s="12" t="s">
-        <v>228</v>
+      <c r="M26" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="N26" s="10" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A27" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E27" t="s">
-        <v>142</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="E27" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F27" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G27" s="2">
@@ -2424,39 +2443,39 @@
       <c r="H27" s="2">
         <v>46387</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K27" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="L27" s="7">
+      <c r="K27" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="L27" s="1">
         <v>46183</v>
       </c>
-      <c r="M27" s="12" t="s">
-        <v>239</v>
+      <c r="M27" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="N27" s="10" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+    <row r="28" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A28" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E28" t="s">
-        <v>142</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="E28" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F28" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G28" s="1">
@@ -2465,39 +2484,39 @@
       <c r="H28" s="1">
         <v>46387</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="L28" s="7">
-        <v>46171</v>
-      </c>
-      <c r="M28" s="12" t="s">
-        <v>238</v>
+      <c r="K28" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="N28" s="10" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A29" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E29" t="s">
-        <v>142</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="E29" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F29" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G29" s="2">
@@ -2506,39 +2525,39 @@
       <c r="H29" s="2">
         <v>46357</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K29" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="L29" s="7">
-        <v>46188</v>
-      </c>
-      <c r="M29" s="12" t="s">
-        <v>223</v>
+      <c r="K29" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="L29" s="1">
+        <v>46192</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>203</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A30" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C30" t="s">
-        <v>182</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="C30" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E30" t="s">
-        <v>142</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="E30" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F30" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G30" s="1">
@@ -2547,39 +2566,39 @@
       <c r="H30" s="1">
         <v>46387</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="K30" s="14" t="s">
+      <c r="K30" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="L30" s="1">
+        <v>46188</v>
+      </c>
+      <c r="M30" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="L30" s="7">
-        <v>46188</v>
-      </c>
-      <c r="M30" s="12" t="s">
-        <v>231</v>
-      </c>
       <c r="N30" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A31" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E31" t="s">
-        <v>142</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="E31" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F31" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G31" s="2">
@@ -2588,39 +2607,39 @@
       <c r="H31" s="2">
         <v>46387</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="K31" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="L31" s="7">
+      <c r="K31" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="L31" s="1">
         <v>46203</v>
       </c>
-      <c r="M31" s="12" t="s">
-        <v>240</v>
+      <c r="M31" s="7" t="s">
+        <v>251</v>
       </c>
       <c r="N31" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+    <row r="32" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A32" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E32" t="s">
-        <v>142</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="E32" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F32" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G32" s="1">
@@ -2629,39 +2648,39 @@
       <c r="H32" s="1">
         <v>46357</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K32" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="L32" s="7">
+      <c r="K32" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="L32" s="1">
         <v>46209</v>
       </c>
-      <c r="M32" s="12" t="s">
-        <v>230</v>
+      <c r="M32" s="7" t="s">
+        <v>210</v>
       </c>
       <c r="N32" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+    <row r="33" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A33" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E33" t="s">
-        <v>142</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="E33" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F33" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G33" s="2">
@@ -2670,39 +2689,39 @@
       <c r="H33" s="2">
         <v>46387</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K33" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="L33" s="7">
+      <c r="K33" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="L33" s="1">
         <v>46240</v>
       </c>
-      <c r="M33" s="12" t="s">
-        <v>223</v>
+      <c r="M33" s="7" t="s">
+        <v>203</v>
       </c>
       <c r="N33" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+    <row r="34" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A34" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C34" t="s">
-        <v>182</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="C34" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G34" s="2">
@@ -2711,39 +2730,39 @@
       <c r="H34" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I34" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="K34" s="14" t="s">
+      <c r="K34" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="L34" s="7" t="s">
+      <c r="L34" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M34" s="12" t="s">
-        <v>235</v>
+      <c r="M34" s="7" t="s">
+        <v>215</v>
       </c>
       <c r="N34" s="10" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A35" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C35" t="s">
-        <v>182</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="C35" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D35" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G35" s="2">
@@ -2752,39 +2771,39 @@
       <c r="H35" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="K35" s="14" t="s">
+      <c r="K35" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="L35" s="7" t="s">
+      <c r="L35" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M35" s="12" t="s">
-        <v>231</v>
+      <c r="M35" s="7" t="s">
+        <v>211</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A36" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E36" t="s">
-        <v>142</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="E36" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F36" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G36" s="1">
@@ -2793,39 +2812,39 @@
       <c r="H36" s="1">
         <v>46357</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="K36" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="L36" s="7">
+      <c r="K36" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="L36" s="1">
         <v>46190</v>
       </c>
-      <c r="M36" s="12" t="s">
-        <v>236</v>
+      <c r="M36" s="7" t="s">
+        <v>216</v>
       </c>
       <c r="N36" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A37" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E37" t="s">
-        <v>142</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="E37" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F37" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G37" s="2">
@@ -2834,39 +2853,39 @@
       <c r="H37" s="2">
         <v>46357</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="K37" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="L37" s="7">
+      <c r="K37" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="L37" s="1">
         <v>46204</v>
       </c>
-      <c r="M37" s="12" t="s">
-        <v>241</v>
+      <c r="M37" s="7" t="s">
+        <v>220</v>
       </c>
       <c r="N37" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+    <row r="38" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A38" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C38" t="s">
-        <v>182</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="C38" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D38" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E38" t="s">
-        <v>142</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="E38" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F38" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G38" s="1">
@@ -2875,39 +2894,39 @@
       <c r="H38" s="1">
         <v>46357</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K38" s="14" t="s">
+      <c r="K38" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="L38" s="7">
+      <c r="L38" s="1">
         <v>46192</v>
       </c>
-      <c r="M38" s="12" t="s">
-        <v>242</v>
+      <c r="M38" s="7" t="s">
+        <v>221</v>
       </c>
       <c r="N38" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A39" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G39" s="2">
@@ -2916,39 +2935,39 @@
       <c r="H39" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I39" t="s">
+      <c r="I39" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="K39" s="14" t="s">
+      <c r="K39" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="L39" s="7" t="s">
+      <c r="L39" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M39" s="12" t="s">
-        <v>243</v>
+      <c r="M39" s="7" t="s">
+        <v>222</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A40" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E40" t="s">
-        <v>142</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="E40" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F40" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G40" s="1">
@@ -2957,39 +2976,39 @@
       <c r="H40" s="1">
         <v>46265</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I40" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K40" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="L40" s="7">
-        <v>46185</v>
-      </c>
-      <c r="M40" s="12" t="s">
-        <v>228</v>
+      <c r="K40" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="L40" s="1">
+        <v>46203</v>
+      </c>
+      <c r="M40" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="N40" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A41" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G41" s="2">
@@ -2998,39 +3017,39 @@
       <c r="H41" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I41" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="K41" s="14" t="s">
+      <c r="K41" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="L41" s="7" t="s">
+      <c r="L41" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M41" s="12" t="s">
+      <c r="M41" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="N41" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="N41" s="10" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+    </row>
+    <row r="42" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A42" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E42" t="s">
-        <v>142</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="E42" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F42" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G42" s="1">
@@ -3039,39 +3058,39 @@
       <c r="H42" s="1">
         <v>46387</v>
       </c>
-      <c r="I42" t="s">
+      <c r="I42" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="K42" s="14" t="s">
+      <c r="K42" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="L42" s="7">
+      <c r="L42" s="1">
         <v>46203</v>
       </c>
-      <c r="M42" s="12" t="s">
-        <v>224</v>
+      <c r="M42" s="7" t="s">
+        <v>204</v>
       </c>
       <c r="N42" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+    <row r="43" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A43" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E43" t="s">
-        <v>142</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="E43" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F43" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G43" s="2">
@@ -3080,39 +3099,39 @@
       <c r="H43" s="2">
         <v>46387</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I43" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K43" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="L43" s="7">
+      <c r="K43" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="L43" s="1">
         <v>46173</v>
       </c>
-      <c r="M43" s="12" t="s">
-        <v>239</v>
+      <c r="M43" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="N43" s="10" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+    <row r="44" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A44" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G44" s="2">
@@ -3121,39 +3140,39 @@
       <c r="H44" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="K44" s="14" t="s">
+      <c r="K44" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="L44" s="7" t="s">
+      <c r="L44" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M44" s="12" t="s">
-        <v>243</v>
+      <c r="M44" s="7" t="s">
+        <v>222</v>
       </c>
       <c r="N44" s="10" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A45" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G45" s="2">
@@ -3162,39 +3181,39 @@
       <c r="H45" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I45" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="K45" s="14" t="s">
+      <c r="K45" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="L45" s="7" t="s">
+      <c r="L45" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M45" s="12" t="s">
-        <v>243</v>
+      <c r="M45" s="7" t="s">
+        <v>222</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A46" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E46" t="s">
-        <v>142</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="E46" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F46" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G46" s="1">
@@ -3203,39 +3222,39 @@
       <c r="H46" s="1">
         <v>46387</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I46" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K46" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="L46" s="7">
+      <c r="K46" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="L46" s="1">
         <v>46183</v>
       </c>
-      <c r="M46" s="12" t="s">
-        <v>239</v>
+      <c r="M46" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="N46" s="10" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+    <row r="47" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A47" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G47" s="2">
@@ -3244,39 +3263,39 @@
       <c r="H47" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I47" t="s">
+      <c r="I47" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="K47" s="14" t="s">
+      <c r="K47" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="L47" s="7" t="s">
+      <c r="L47" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M47" s="12" t="s">
-        <v>244</v>
+      <c r="M47" s="7" t="s">
+        <v>223</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A48" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E48" t="s">
-        <v>142</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="E48" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F48" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G48" s="1">
@@ -3285,39 +3304,39 @@
       <c r="H48" s="1">
         <v>46387</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I48" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K48" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="L48" s="7">
-        <v>46188</v>
-      </c>
-      <c r="M48" s="12" t="s">
-        <v>224</v>
+      <c r="K48" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="L48" s="1">
+        <v>46189</v>
+      </c>
+      <c r="M48" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="N48" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A49" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G49" s="2">
@@ -3326,39 +3345,39 @@
       <c r="H49" s="2">
         <v>46166</v>
       </c>
-      <c r="I49" t="s">
+      <c r="I49" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K49" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="L49" s="7">
-        <v>46176</v>
-      </c>
-      <c r="M49" s="12" t="s">
-        <v>228</v>
+      <c r="K49" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="L49" s="1">
+        <v>46203</v>
+      </c>
+      <c r="M49" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A50" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E50" t="s">
-        <v>142</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="E50" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F50" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G50" s="1">
@@ -3367,39 +3386,39 @@
       <c r="H50" s="1">
         <v>46357</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I50" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K50" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="L50" s="7">
-        <v>46188</v>
-      </c>
-      <c r="M50" s="12" t="s">
-        <v>228</v>
+      <c r="K50" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="L50" s="1">
+        <v>46192</v>
+      </c>
+      <c r="M50" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="N50" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A51" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E51" t="s">
-        <v>142</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="E51" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F51" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G51" s="2">
@@ -3408,39 +3427,39 @@
       <c r="H51" s="2">
         <v>46387</v>
       </c>
-      <c r="I51" t="s">
+      <c r="I51" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K51" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="L51" s="7">
-        <v>46185</v>
-      </c>
-      <c r="M51" s="12" t="s">
-        <v>224</v>
+      <c r="K51" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="L51" s="1">
+        <v>46199</v>
+      </c>
+      <c r="M51" s="7" t="s">
+        <v>204</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A52" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E52" t="s">
-        <v>177</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="E52" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F52" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G52" s="1">
@@ -3449,80 +3468,80 @@
       <c r="H52" s="1">
         <v>46204</v>
       </c>
-      <c r="I52" t="s">
+      <c r="I52" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K52" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="L52" s="7">
-        <v>46188</v>
-      </c>
-      <c r="M52" s="12" t="s">
-        <v>228</v>
+      <c r="K52" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="L52" s="1">
+        <v>46203</v>
+      </c>
+      <c r="M52" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="N52" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A53" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E53" t="s">
-        <v>142</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="E53" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F53" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G53" s="2">
         <v>46082</v>
       </c>
-      <c r="H53" s="2">
-        <v>46387</v>
-      </c>
-      <c r="I53" t="s">
-        <v>146</v>
-      </c>
-      <c r="K53" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="L53" s="7">
-        <v>46234</v>
-      </c>
-      <c r="M53" s="12" t="s">
-        <v>228</v>
+      <c r="H53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="K53" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M53" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A54" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E54" t="s">
-        <v>142</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="E54" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F54" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G54" s="3">
@@ -3531,39 +3550,39 @@
       <c r="H54" s="3">
         <v>46387</v>
       </c>
-      <c r="I54" t="s">
+      <c r="I54" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="K54" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="L54" s="7">
+      <c r="K54" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="L54" s="1">
         <v>46248</v>
       </c>
-      <c r="M54" s="12" t="s">
-        <v>245</v>
+      <c r="M54" s="7" t="s">
+        <v>224</v>
       </c>
       <c r="N54" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
+    <row r="55" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A55" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E55" t="s">
-        <v>142</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="E55" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F55" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G55" s="2">
@@ -3572,39 +3591,39 @@
       <c r="H55" s="3">
         <v>46387</v>
       </c>
-      <c r="I55" t="s">
+      <c r="I55" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="K55" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="L55" s="7">
+      <c r="K55" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="L55" s="1">
         <v>46197</v>
       </c>
-      <c r="M55" s="12" t="s">
-        <v>229</v>
+      <c r="M55" s="7" t="s">
+        <v>209</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A56" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E56" t="s">
-        <v>142</v>
-      </c>
-      <c r="F56" t="s">
+      <c r="E56" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F56" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G56" s="1">
@@ -3613,39 +3632,39 @@
       <c r="H56" s="3">
         <v>46387</v>
       </c>
-      <c r="I56" t="s">
-        <v>146</v>
-      </c>
-      <c r="K56" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="L56" s="7">
-        <v>46209</v>
-      </c>
-      <c r="M56" s="12" t="s">
-        <v>224</v>
+      <c r="I56" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="K56" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="L56" s="1">
+        <v>46234</v>
+      </c>
+      <c r="M56" s="7" t="s">
+        <v>204</v>
       </c>
       <c r="N56" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
+    <row r="57" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A57" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E57" t="s">
-        <v>177</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="E57" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F57" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G57" s="2">
@@ -3654,39 +3673,39 @@
       <c r="H57" s="2">
         <v>46204</v>
       </c>
-      <c r="I57" t="s">
+      <c r="I57" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="K57" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="L57" s="7">
+      <c r="K57" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="L57" s="1">
         <v>46204</v>
       </c>
-      <c r="M57" s="12" t="s">
-        <v>228</v>
+      <c r="M57" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="N57" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
+    <row r="58" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A58" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E58" t="s">
-        <v>177</v>
-      </c>
-      <c r="F58" t="s">
+      <c r="E58" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F58" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G58" s="3">
@@ -3695,39 +3714,39 @@
       <c r="H58" s="3">
         <v>46203</v>
       </c>
-      <c r="I58" t="s">
+      <c r="I58" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K58" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="L58" s="7">
+      <c r="K58" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="L58" s="1">
         <v>46188</v>
       </c>
-      <c r="M58" s="12" t="s">
-        <v>239</v>
+      <c r="M58" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="N58" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A59" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E59" t="s">
-        <v>142</v>
-      </c>
-      <c r="F59" t="s">
+      <c r="E59" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F59" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G59" s="3">
@@ -3736,39 +3755,39 @@
       <c r="H59" s="2">
         <v>46387</v>
       </c>
-      <c r="I59" t="s">
+      <c r="I59" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K59" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="L59" s="7">
-        <v>46178</v>
-      </c>
-      <c r="M59" s="12" t="s">
-        <v>229</v>
+      <c r="K59" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="L59" s="1">
+        <v>46203</v>
+      </c>
+      <c r="M59" s="7" t="s">
+        <v>209</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A60" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D60" t="s">
-        <v>183</v>
-      </c>
-      <c r="E60" t="s">
-        <v>142</v>
-      </c>
-      <c r="F60" t="s">
+      <c r="D60" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F60" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G60" s="3">
@@ -3777,39 +3796,39 @@
       <c r="H60" s="3">
         <v>46387</v>
       </c>
-      <c r="I60" t="s">
+      <c r="I60" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K60" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="L60" s="8">
-        <v>46188</v>
-      </c>
-      <c r="M60" s="12" t="s">
-        <v>228</v>
+      <c r="K60" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="L60" s="3">
+        <v>46195</v>
+      </c>
+      <c r="M60" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="N60" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A61" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D61" t="s">
-        <v>183</v>
-      </c>
-      <c r="E61" t="s">
-        <v>142</v>
-      </c>
-      <c r="F61" t="s">
+      <c r="D61" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F61" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G61" s="3">
@@ -3818,39 +3837,39 @@
       <c r="H61" s="3">
         <v>46564</v>
       </c>
-      <c r="I61" t="s">
+      <c r="I61" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K61" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="L61" s="8">
-        <v>46185</v>
-      </c>
-      <c r="M61" s="12" t="s">
-        <v>224</v>
+      <c r="K61" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="L61" s="3">
+        <v>46189</v>
+      </c>
+      <c r="M61" s="7" t="s">
+        <v>204</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" ht="16" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A62" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D62" t="s">
-        <v>183</v>
-      </c>
-      <c r="E62" t="s">
-        <v>142</v>
-      </c>
-      <c r="F62" t="s">
+      <c r="D62" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F62" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G62" s="3">
@@ -3859,39 +3878,39 @@
       <c r="H62" s="3">
         <v>46387</v>
       </c>
-      <c r="I62" t="s">
+      <c r="I62" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K62" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L62" s="7">
+      <c r="K62" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="L62" s="1">
         <v>46183</v>
       </c>
-      <c r="M62" s="12" t="s">
-        <v>243</v>
+      <c r="M62" s="7" t="s">
+        <v>222</v>
       </c>
       <c r="N62" s="10" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" t="s">
+    <row r="63" spans="1:14" s="9" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F63" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G63" s="4">
@@ -3900,39 +3919,39 @@
       <c r="H63" s="4">
         <v>46083</v>
       </c>
-      <c r="I63" t="s">
+      <c r="I63" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K63" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="L63" s="9">
-        <v>46189</v>
-      </c>
-      <c r="M63" s="12" t="s">
-        <v>246</v>
+      <c r="K63" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="L63" s="4">
+        <v>46190</v>
+      </c>
+      <c r="M63" s="7" t="s">
+        <v>252</v>
       </c>
       <c r="N63" s="10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B64" s="9" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" t="s">
-        <v>180</v>
-      </c>
-      <c r="B64" t="s">
-        <v>181</v>
-      </c>
-      <c r="C64" t="s">
+      <c r="C64" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D64" t="s">
-        <v>183</v>
-      </c>
-      <c r="E64" t="s">
-        <v>142</v>
-      </c>
-      <c r="F64" t="s">
+      <c r="D64" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F64" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G64" s="11">
@@ -3941,95 +3960,62 @@
       <c r="H64" s="11">
         <v>46568</v>
       </c>
-      <c r="I64" t="s">
+      <c r="I64" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K64" s="15" t="s">
-        <v>197</v>
+      <c r="K64" s="9" t="s">
+        <v>187</v>
       </c>
       <c r="L64" s="11">
         <v>46215</v>
       </c>
-      <c r="M64" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="N64" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="65" spans="7:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G65" s="11"/>
-      <c r="H65" s="11"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="13"/>
+      <c r="M64" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="N64" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="G65" s="11">
+        <v>46184</v>
+      </c>
+      <c r="H65" s="11">
+        <v>46387</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="K65" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="L65" s="11">
+        <v>46184</v>
+      </c>
+      <c r="M65" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="N65" s="9" t="s">
+        <v>144</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="M2" r:id="rId1" display="mailto:Diego.RochaSantos@claro.com.br" xr:uid="{D0338977-67C9-4B5B-9644-A9AE82FD389E}"/>
-    <hyperlink ref="M3" r:id="rId2" xr:uid="{E09EF2DC-D941-4EBA-B94F-54B57EC16277}"/>
-    <hyperlink ref="M4" r:id="rId3" display="mailto:paulo.rocha@claro.com.br" xr:uid="{C34DFE80-3C23-4DD3-AC81-66A0DCEF8A94}"/>
-    <hyperlink ref="M5" r:id="rId4" display="mailto:alex.lencione@claro.com.br" xr:uid="{DF78BD93-58E9-43C7-BCA7-408B89E8E5C4}"/>
-    <hyperlink ref="M6" r:id="rId5" display="mailto:gustavo.mendes@claro.com.br" xr:uid="{63F7BCA6-A107-4888-A9EC-EA28CEE7215E}"/>
-    <hyperlink ref="M7" r:id="rId6" display="mailto:Santos.PBruno@claro.com.br" xr:uid="{B57B225A-4CD8-41D3-903C-BD08AB7F397D}"/>
-    <hyperlink ref="M8" r:id="rId7" display="mailto:Marcelo.Saleme@claro.com.br" xr:uid="{DA5A61AE-0FCC-4357-82F9-F9B7EEC68367}"/>
-    <hyperlink ref="M9" r:id="rId8" display="mailto:helder.ssilva@claro.com.br" xr:uid="{46C1BE56-FE3E-4951-8E18-4EBDD5F3E9F6}"/>
-    <hyperlink ref="M10" r:id="rId9" display="mailto:fabio.ocosta@claro.com.br" xr:uid="{4D13D19D-8EDA-4153-B705-8095CC135355}"/>
-    <hyperlink ref="M11" r:id="rId10" display="mailto:alex.lencione@claro.com.br" xr:uid="{DF428FB2-9347-474C-AEDE-0AB502DB0C71}"/>
-    <hyperlink ref="M12" r:id="rId11" display="mailto:evandro.moratori@claro.com.br" xr:uid="{7C272197-F243-4F22-AAA2-CFE5B6F88A65}"/>
-    <hyperlink ref="M13" r:id="rId12" display="mailto:ADEMILSON.SILVA@claro.com.br" xr:uid="{7ED071AF-E6D5-4E3F-9578-49B6C1C270BB}"/>
-    <hyperlink ref="M14" r:id="rId13" display="mailto:evandro.moratori@claro.com.br" xr:uid="{56BE6A5A-4D9E-470F-A1A9-94B619760DDD}"/>
-    <hyperlink ref="M15" r:id="rId14" display="mailto:gustavo.mendes@claro.com.br" xr:uid="{941FB5CF-53C6-45BC-9B8C-BE6E0CE9D031}"/>
-    <hyperlink ref="M16" r:id="rId15" display="mailto:leandro.carlos@claro.com.br" xr:uid="{259FE933-C362-484B-B667-4286E2E2198F}"/>
-    <hyperlink ref="M17" r:id="rId16" display="mailto:Jefferson.Santana@claro.com.br" xr:uid="{09E56FDA-5160-4B4D-8AAE-AC4F5F4198BA}"/>
-    <hyperlink ref="M18" r:id="rId17" display="mailto:Marileia.Passos@claro.com.br" xr:uid="{7C6F35D5-7371-4C32-B887-E0992A4F200F}"/>
-    <hyperlink ref="M19" r:id="rId18" display="mailto:fabiana.pons@claro.com.br" xr:uid="{D7C6E116-3145-4A19-B9DB-AF4A21B00D36}"/>
-    <hyperlink ref="M20" r:id="rId19" display="mailto:jeferson.teixeira@claro.com.br" xr:uid="{5E761672-0D7B-4D56-9721-A85389B5FBB9}"/>
-    <hyperlink ref="M21" r:id="rId20" display="mailto:Fabio.Lima@claro.com.br" xr:uid="{4855793E-10AA-4017-80B5-409CA412790F}"/>
-    <hyperlink ref="M22" r:id="rId21" display="mailto:cleria.plaster@claro.com.br" xr:uid="{FBDE0093-DFCB-4F48-9E6C-85A4E2995A28}"/>
-    <hyperlink ref="M23" r:id="rId22" display="mailto:alex.lencione@claro.com.br" xr:uid="{53B43FA3-4639-4A44-9665-05705A709776}"/>
-    <hyperlink ref="M24" r:id="rId23" display="mailto:alex.lencione@claro.com.br" xr:uid="{46A974B6-4E32-4938-86D5-7FD77F8D0A34}"/>
-    <hyperlink ref="M25" r:id="rId24" display="mailto:fabio.ocosta@claro.com.br" xr:uid="{94C61E69-AD27-43A7-A134-1168360F5752}"/>
-    <hyperlink ref="M26" r:id="rId25" display="mailto:helder.ssilva@claro.com.br" xr:uid="{79F1415A-3E9B-496C-A286-0164E2AA8231}"/>
-    <hyperlink ref="M27" r:id="rId26" display="mailto:ingrid.alcici@claro.com.br" xr:uid="{2C50D036-1EB9-4277-92CA-AC8855B444F3}"/>
-    <hyperlink ref="M28" r:id="rId27" display="mailto:cleria.plaster@claro.com.br" xr:uid="{5CE4CED0-B155-42F0-AE2E-660CCDE56D2E}"/>
-    <hyperlink ref="M29" r:id="rId28" display="mailto:paulo.rocha@claro.com.br" xr:uid="{90FD2906-7798-4B01-8097-17E693BD6414}"/>
-    <hyperlink ref="M30" r:id="rId29" display="mailto:ADEMILSON.SILVA@claro.com.br" xr:uid="{621E0011-519D-4EC7-B1D1-AEB991CD94BD}"/>
-    <hyperlink ref="M31" r:id="rId30" display="mailto:Marinalva.Marculino@claro.com.br;" xr:uid="{E6BE150A-F8EB-4E2A-8915-7CAB6A315A59}"/>
-    <hyperlink ref="M32" r:id="rId31" display="mailto:evandro.moratori@claro.com.br" xr:uid="{C78461C4-4E3C-45ED-8C89-43D70803BFA4}"/>
-    <hyperlink ref="M33" r:id="rId32" display="mailto:paulo.rocha@claro.com.br" xr:uid="{67182857-242E-469F-8E06-F30E781D8AAF}"/>
-    <hyperlink ref="M34" r:id="rId33" display="mailto:fabiana.pons@claro.com.br" xr:uid="{69BF57C9-44EC-4FDF-A4F9-F66FEA206385}"/>
-    <hyperlink ref="M35" r:id="rId34" display="mailto:ADEMILSON.SILVA@claro.com.br" xr:uid="{E3BC9E2D-F27D-4730-A178-0B474FBD9149}"/>
-    <hyperlink ref="M36" r:id="rId35" display="mailto:jeferson.teixeira@claro.com.br" xr:uid="{2C6CF1C4-42F4-4346-9937-2C5DC27F7CD0}"/>
-    <hyperlink ref="M37" r:id="rId36" display="mailto:Ildo.Lima@claro.com.br" xr:uid="{E88A99F8-9C35-4F60-8E70-EF232F4F5872}"/>
-    <hyperlink ref="M38" r:id="rId37" display="mailto:LUCAS.RIBEIRO@claro.com.br" xr:uid="{CB5988CA-92B0-4D31-BEF5-8139ECCFEA4C}"/>
-    <hyperlink ref="M39" r:id="rId38" display="mailto:Bernardino.lagoa@claro.com.br" xr:uid="{46CB1D2D-94F6-4B35-B42E-2835672E7C19}"/>
-    <hyperlink ref="M40" r:id="rId39" display="mailto:helder.ssilva@claro.com.br" xr:uid="{AB5D15D7-D11A-487A-90C4-28B274F334AE}"/>
-    <hyperlink ref="M41" r:id="rId40" display="mailto:gustavo.mendes@claro.com.br" xr:uid="{9F452B28-DEA9-4DAA-9F6D-ABFA227B083E}"/>
-    <hyperlink ref="M42" r:id="rId41" display="mailto:alex.lencione@claro.com.br" xr:uid="{790A0E09-7B97-4506-9422-C5C1F144CFBA}"/>
-    <hyperlink ref="M43" r:id="rId42" display="mailto:ingrid.alcici@claro.com.br" xr:uid="{AC8B0501-4109-4CA6-A8D7-E4FB80461C49}"/>
-    <hyperlink ref="M44" r:id="rId43" display="mailto:Bernardino.lagoa@claro.com.br" xr:uid="{94459F01-FC2B-46C5-8FE2-80D59B854FB5}"/>
-    <hyperlink ref="M45" r:id="rId44" display="mailto:Bernardino.lagoa@claro.com.br" xr:uid="{BCAF3998-3548-40DC-AB35-1060918ACDFD}"/>
-    <hyperlink ref="M46" r:id="rId45" display="mailto:ingrid.alcici@claro.com.br" xr:uid="{28E38E96-F974-4102-B176-422BC834A7AF}"/>
-    <hyperlink ref="M47" r:id="rId46" display="mailto:marcelo.paulino@claro.com.br" xr:uid="{66441BF5-FA70-4A07-A84D-54C5A4A13C53}"/>
-    <hyperlink ref="M48" r:id="rId47" display="mailto:alex.lencione@claro.com.br" xr:uid="{786C11C0-2EF4-4D58-ACDE-6958F7F65CA6}"/>
-    <hyperlink ref="M49" r:id="rId48" display="mailto:helder.ssilva@claro.com.br" xr:uid="{EF293E7E-34A1-4FA8-991A-CBA0C9C393FD}"/>
-    <hyperlink ref="M50" r:id="rId49" display="mailto:helder.ssilva@claro.com.br" xr:uid="{5BA8B0C7-5139-476C-9D11-4C1D7877287A}"/>
-    <hyperlink ref="M51" r:id="rId50" display="mailto:alex.lencione@claro.com.br" xr:uid="{6AD418E0-6F5F-4BA5-BD0A-91C395D7CF7A}"/>
-    <hyperlink ref="M52" r:id="rId51" display="mailto:helder.ssilva@claro.com.br" xr:uid="{75327529-5FE8-4F8E-91E2-DC4FCCF8E070}"/>
-    <hyperlink ref="M53" r:id="rId52" display="mailto:helder.ssilva@claro.com.br" xr:uid="{945C7092-C6C0-4E6A-8148-A8B153C007E4}"/>
-    <hyperlink ref="M54" r:id="rId53" display="mailto:fabricio.friolani@claro.com.br" xr:uid="{8DA1F76A-7786-49A2-BF6C-2D2F20D7A657}"/>
-    <hyperlink ref="M55" r:id="rId54" display="mailto:fabio.ocosta@claro.com.br" xr:uid="{4A4F335F-4E12-4977-954C-3483F31020DD}"/>
-    <hyperlink ref="M56" r:id="rId55" display="mailto:alex.lencione@claro.com.br" xr:uid="{CF236626-4501-4B8B-83E1-239CDD4AC2EB}"/>
-    <hyperlink ref="M57" r:id="rId56" display="mailto:helder.ssilva@claro.com.br" xr:uid="{948BC221-13A1-4694-8F57-53BD5C98FD95}"/>
-    <hyperlink ref="M58" r:id="rId57" display="mailto:ingrid.alcici@claro.com.br" xr:uid="{E2EC81F5-F91F-4A9F-BC7E-875D745D8341}"/>
-    <hyperlink ref="M59" r:id="rId58" display="mailto:fabio.ocosta@claro.com.br" xr:uid="{6B4FCDA5-F27F-4ECF-9FB3-6B2A47E0B4DF}"/>
-    <hyperlink ref="M60" r:id="rId59" display="mailto:helder.ssilva@claro.com.br" xr:uid="{5EB64C13-83DB-435D-BA20-DC0A87B82F25}"/>
-    <hyperlink ref="M61" r:id="rId60" display="mailto:alex.lencione@claro.com.br" xr:uid="{60536BF0-F76D-4042-A469-91A768A4C6E3}"/>
-    <hyperlink ref="M62" r:id="rId61" display="mailto:Bernardino.lagoa@claro.com.br" xr:uid="{5164CF39-CB99-46E2-98AB-6925F0CCED92}"/>
-    <hyperlink ref="M63" r:id="rId62" display="mailto:Bernardino.lagoa@claro.com.br,Bruno.Feijo@claro.com.br" xr:uid="{4606E8EE-F97F-4D0A-A1E5-BA36AA180B25}"/>
-    <hyperlink ref="M64" r:id="rId63" display="mailto:paulo.rocha@claro.com.br" xr:uid="{E0A00782-EA79-4CE3-94A7-F14E6B4CD6D9}"/>
-  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -4044,17 +4030,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="48a4df2c-25c0-4bd5-9ad3-969cdc4eb0ad">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fe5609ce-cb92-4045-944c-c105fdf4b20b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006A0F678961C25F42A60818D832EED552" ma:contentTypeVersion="15" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="dc2a7ab8599bba470a78deafa62af16c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="48a4df2c-25c0-4bd5-9ad3-969cdc4eb0ad" xmlns:ns3="fe5609ce-cb92-4045-944c-c105fdf4b20b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ffd182497d787a9e927f0f89c1000013" ns2:_="" ns3:_="">
     <xsd:import namespace="48a4df2c-25c0-4bd5-9ad3-969cdc4eb0ad"/>
@@ -4289,6 +4264,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="48a4df2c-25c0-4bd5-9ad3-969cdc4eb0ad">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fe5609ce-cb92-4045-944c-c105fdf4b20b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{421192A4-7E63-4E34-BFD9-A0D092033413}">
   <ds:schemaRefs>
@@ -4298,17 +4284,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F58F0C4-7563-4480-B156-7EBAF344CD6A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="48a4df2c-25c0-4bd5-9ad3-969cdc4eb0ad"/>
-    <ds:schemaRef ds:uri="fe5609ce-cb92-4045-944c-c105fdf4b20b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4FC87EE-D01F-4F08-8D84-C3D05E1D5A3A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4325,4 +4300,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F58F0C4-7563-4480-B156-7EBAF344CD6A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="48a4df2c-25c0-4bd5-9ad3-969cdc4eb0ad"/>
+    <ds:schemaRef ds:uri="fe5609ce-cb92-4045-944c-c105fdf4b20b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>